--- a/research/traditional_assets/database/data/egypt/egypt_recreation.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_recreation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1744415422260374</v>
+        <v>0.1740839237560288</v>
       </c>
       <c r="C2">
-        <v>1397.461028278093</v>
+        <v>1388.262584459667</v>
       </c>
       <c r="D2">
-        <v>1381.261028278093</v>
+        <v>1385.111584459667</v>
       </c>
       <c r="E2">
-        <v>-525.2</v>
+        <v>-512.1510000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.049</v>
       </c>
       <c r="G2">
         <v>16.2</v>
@@ -1445,28 +1445,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6563647</v>
       </c>
       <c r="N2">
-        <v>71.30000000000001</v>
+        <v>70.64363530000001</v>
       </c>
       <c r="O2">
-        <v>16.0425</v>
+        <v>15.8948179425</v>
       </c>
       <c r="P2">
-        <v>55.25750000000001</v>
+        <v>54.74881735750001</v>
       </c>
       <c r="Q2">
-        <v>80.45750000000001</v>
+        <v>79.9488173575</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1744415422260374</v>
+        <v>0.1754485846020493</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378595</v>
+        <v>0.9039673084548981</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>108.6286328317169</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1740839237560288</v>
+        <v>0.1737263052860203</v>
       </c>
       <c r="C3">
-        <v>1388.262584459667</v>
+        <v>1379.085669129963</v>
       </c>
       <c r="D3">
-        <v>1385.111584459667</v>
+        <v>1388.983669129963</v>
       </c>
       <c r="E3">
-        <v>-512.1510000000001</v>
+        <v>-499.102</v>
       </c>
       <c r="F3">
-        <v>13.049</v>
+        <v>26.098</v>
       </c>
       <c r="G3">
         <v>16.2</v>
@@ -1527,28 +1527,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M3">
-        <v>0.6563647</v>
+        <v>1.3127294</v>
       </c>
       <c r="N3">
-        <v>70.64363530000001</v>
+        <v>69.98727060000002</v>
       </c>
       <c r="O3">
-        <v>15.8948179425</v>
+        <v>15.747135885</v>
       </c>
       <c r="P3">
-        <v>54.74881735750001</v>
+        <v>54.24013471500001</v>
       </c>
       <c r="Q3">
-        <v>79.9488173575</v>
+        <v>79.440134715</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1754485846020493</v>
+        <v>0.176476178863286</v>
       </c>
       <c r="T3">
-        <v>0.9039673084548981</v>
+        <v>0.9111321504110602</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>108.6286328317169</v>
+        <v>54.31431641585845</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1737263052860203</v>
+        <v>0.1733686868160117</v>
       </c>
       <c r="C4">
-        <v>1379.085669129963</v>
+        <v>1369.930463344037</v>
       </c>
       <c r="D4">
-        <v>1388.983669129963</v>
+        <v>1392.877463344037</v>
       </c>
       <c r="E4">
-        <v>-499.102</v>
+        <v>-486.0530000000001</v>
       </c>
       <c r="F4">
-        <v>26.098</v>
+        <v>39.147</v>
       </c>
       <c r="G4">
         <v>16.2</v>
@@ -1609,28 +1609,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M4">
-        <v>1.3127294</v>
+        <v>1.9690941</v>
       </c>
       <c r="N4">
-        <v>69.98727060000002</v>
+        <v>69.3309059</v>
       </c>
       <c r="O4">
-        <v>15.747135885</v>
+        <v>15.5994538275</v>
       </c>
       <c r="P4">
-        <v>54.24013471500001</v>
+        <v>53.73145207250001</v>
       </c>
       <c r="Q4">
-        <v>79.440134715</v>
+        <v>78.93145207250001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.176476178863286</v>
+        <v>0.1775249606350636</v>
       </c>
       <c r="T4">
-        <v>0.9111321504110602</v>
+        <v>0.9184447210673493</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.31431641585845</v>
+        <v>36.20954427723897</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1733686868160117</v>
+        <v>0.1730110683460031</v>
       </c>
       <c r="C5">
-        <v>1369.930463344037</v>
+        <v>1360.797150192886</v>
       </c>
       <c r="D5">
-        <v>1392.877463344037</v>
+        <v>1396.793150192886</v>
       </c>
       <c r="E5">
-        <v>-486.0530000000001</v>
+        <v>-473.004</v>
       </c>
       <c r="F5">
-        <v>39.147</v>
+        <v>52.19600000000001</v>
       </c>
       <c r="G5">
         <v>16.2</v>
@@ -1691,28 +1691,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M5">
-        <v>1.9690941</v>
+        <v>2.6254588</v>
       </c>
       <c r="N5">
-        <v>69.3309059</v>
+        <v>68.67454120000001</v>
       </c>
       <c r="O5">
-        <v>15.5994538275</v>
+        <v>15.45177177</v>
       </c>
       <c r="P5">
-        <v>53.73145207250001</v>
+        <v>53.22276943000001</v>
       </c>
       <c r="Q5">
-        <v>78.93145207250001</v>
+        <v>78.42276943</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1775249606350636</v>
+        <v>0.1785955920270866</v>
       </c>
       <c r="T5">
-        <v>0.9184447210673493</v>
+        <v>0.9259096369456444</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.20954427723897</v>
+        <v>27.15715820792922</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1730110683460031</v>
+        <v>0.1726534498759945</v>
       </c>
       <c r="C6">
-        <v>1360.797150192886</v>
+        <v>1351.685914832151</v>
       </c>
       <c r="D6">
-        <v>1396.793150192886</v>
+        <v>1400.730914832151</v>
       </c>
       <c r="E6">
-        <v>-473.004</v>
+        <v>-459.955</v>
       </c>
       <c r="F6">
-        <v>52.19600000000001</v>
+        <v>65.245</v>
       </c>
       <c r="G6">
         <v>16.2</v>
@@ -1773,28 +1773,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M6">
-        <v>2.6254588</v>
+        <v>3.2818235</v>
       </c>
       <c r="N6">
-        <v>68.67454120000001</v>
+        <v>68.01817650000001</v>
       </c>
       <c r="O6">
-        <v>15.45177177</v>
+        <v>15.3040897125</v>
       </c>
       <c r="P6">
-        <v>53.22276943000001</v>
+        <v>52.71408678750001</v>
       </c>
       <c r="Q6">
-        <v>78.42276943</v>
+        <v>77.9140867875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1785955920270866</v>
+        <v>0.1796887630273626</v>
       </c>
       <c r="T6">
-        <v>0.9259096369456444</v>
+        <v>0.9335317089476932</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.15715820792922</v>
+        <v>21.72572656634338</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1726534498759945</v>
+        <v>0.1722958314059859</v>
       </c>
       <c r="C7">
-        <v>1351.685914832151</v>
+        <v>1342.596944511297</v>
       </c>
       <c r="D7">
-        <v>1400.730914832151</v>
+        <v>1404.690944511297</v>
       </c>
       <c r="E7">
-        <v>-459.955</v>
+        <v>-446.9060000000001</v>
       </c>
       <c r="F7">
-        <v>65.245</v>
+        <v>78.29400000000001</v>
       </c>
       <c r="G7">
         <v>16.2</v>
@@ -1855,28 +1855,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M7">
-        <v>3.2818235</v>
+        <v>3.9381882</v>
       </c>
       <c r="N7">
-        <v>68.01817650000001</v>
+        <v>67.36181180000001</v>
       </c>
       <c r="O7">
-        <v>15.3040897125</v>
+        <v>15.156407655</v>
       </c>
       <c r="P7">
-        <v>52.71408678750001</v>
+        <v>52.20540414500001</v>
       </c>
       <c r="Q7">
-        <v>77.9140867875</v>
+        <v>77.40540414500001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1796887630273626</v>
+        <v>0.1808051929850914</v>
       </c>
       <c r="T7">
-        <v>0.9335317089476932</v>
+        <v>0.9413159526944663</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.72572656634338</v>
+        <v>18.10477213861948</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1722958314059859</v>
+        <v>0.1719382129359774</v>
       </c>
       <c r="C8">
-        <v>1342.596944511297</v>
+        <v>1333.530428603299</v>
       </c>
       <c r="D8">
-        <v>1404.690944511297</v>
+        <v>1408.673428603299</v>
       </c>
       <c r="E8">
-        <v>-446.9060000000001</v>
+        <v>-433.857</v>
       </c>
       <c r="F8">
-        <v>78.294</v>
+        <v>91.343</v>
       </c>
       <c r="G8">
         <v>16.2</v>
@@ -1937,28 +1937,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M8">
-        <v>3.938188199999999</v>
+        <v>4.5945529</v>
       </c>
       <c r="N8">
-        <v>67.36181180000001</v>
+        <v>66.70544710000001</v>
       </c>
       <c r="O8">
-        <v>15.156407655</v>
+        <v>15.0087255975</v>
       </c>
       <c r="P8">
-        <v>52.20540414500001</v>
+        <v>51.69672150250001</v>
       </c>
       <c r="Q8">
-        <v>77.40540414500001</v>
+        <v>76.89672150250001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1808051929850914</v>
+        <v>0.181945632189223</v>
       </c>
       <c r="T8">
-        <v>0.9413159526944663</v>
+        <v>0.949267599532568</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.10477213861948</v>
+        <v>15.5183761188167</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1719382129359773</v>
+        <v>0.1715805944659688</v>
       </c>
       <c r="C9">
-        <v>1333.530428603299</v>
+        <v>1324.486558634825</v>
       </c>
       <c r="D9">
-        <v>1408.673428603299</v>
+        <v>1412.678558634825</v>
       </c>
       <c r="E9">
-        <v>-433.857</v>
+        <v>-420.808</v>
       </c>
       <c r="F9">
-        <v>91.34300000000002</v>
+        <v>104.392</v>
       </c>
       <c r="G9">
         <v>16.2</v>
@@ -2019,28 +2019,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M9">
-        <v>4.594552900000001</v>
+        <v>5.2509176</v>
       </c>
       <c r="N9">
-        <v>66.70544710000001</v>
+        <v>66.04908240000002</v>
       </c>
       <c r="O9">
-        <v>15.0087255975</v>
+        <v>14.86104354</v>
       </c>
       <c r="P9">
-        <v>51.69672150250001</v>
+        <v>51.18803886000001</v>
       </c>
       <c r="Q9">
-        <v>76.89672150250001</v>
+        <v>76.38803886000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.181945632189223</v>
+        <v>0.1831108635499661</v>
       </c>
       <c r="T9">
-        <v>0.949267599532568</v>
+        <v>0.9573921082584543</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.5183761188167</v>
+        <v>13.57857910396461</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1715805944659688</v>
+        <v>0.1713276009959602</v>
       </c>
       <c r="C10">
-        <v>1324.486558634825</v>
+        <v>1314.284728880413</v>
       </c>
       <c r="D10">
-        <v>1412.678558634825</v>
+        <v>1415.525728880413</v>
       </c>
       <c r="E10">
-        <v>-420.808</v>
+        <v>-407.759</v>
       </c>
       <c r="F10">
-        <v>104.392</v>
+        <v>117.441</v>
       </c>
       <c r="G10">
         <v>16.2</v>
@@ -2101,45 +2101,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M10">
-        <v>5.2509176</v>
+        <v>6.0834438</v>
       </c>
       <c r="N10">
-        <v>66.04908240000002</v>
+        <v>65.21655620000001</v>
       </c>
       <c r="O10">
-        <v>14.86104354</v>
+        <v>14.673725145</v>
       </c>
       <c r="P10">
-        <v>51.18803886000001</v>
+        <v>50.54283105500001</v>
       </c>
       <c r="Q10">
-        <v>76.38803886000001</v>
+        <v>75.74283105500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1831108635499661</v>
+        <v>0.184301704391165</v>
       </c>
       <c r="T10">
-        <v>0.9573921082584543</v>
+        <v>0.9656951776156789</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.225</v>
       </c>
       <c r="W10">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.57857910396461</v>
+        <v>11.72033511676396</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1713276009959602</v>
+        <v>0.1709816075259516</v>
       </c>
       <c r="C11">
-        <v>1314.284728880413</v>
+        <v>1305.148145955902</v>
       </c>
       <c r="D11">
-        <v>1415.525728880413</v>
+        <v>1419.438145955902</v>
       </c>
       <c r="E11">
-        <v>-407.759</v>
+        <v>-394.71</v>
       </c>
       <c r="F11">
-        <v>117.441</v>
+        <v>130.49</v>
       </c>
       <c r="G11">
         <v>16.2</v>
@@ -2183,28 +2183,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M11">
-        <v>6.0834438</v>
+        <v>6.759382</v>
       </c>
       <c r="N11">
-        <v>65.21655620000001</v>
+        <v>64.54061800000001</v>
       </c>
       <c r="O11">
-        <v>14.673725145</v>
+        <v>14.52163905</v>
       </c>
       <c r="P11">
-        <v>50.54283105500001</v>
+        <v>50.01897895</v>
       </c>
       <c r="Q11">
-        <v>75.74283105500001</v>
+        <v>75.21897895000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.184301704391165</v>
+        <v>0.1855190083621684</v>
       </c>
       <c r="T11">
-        <v>0.9656951776156789</v>
+        <v>0.9741827596252862</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.72033511676396</v>
+        <v>10.54830160508757</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1709816075259516</v>
+        <v>0.170780539055943</v>
       </c>
       <c r="C12">
-        <v>1305.148145955902</v>
+        <v>1294.382735532609</v>
       </c>
       <c r="D12">
-        <v>1419.438145955902</v>
+        <v>1421.721735532609</v>
       </c>
       <c r="E12">
-        <v>-394.71</v>
+        <v>-381.6610000000001</v>
       </c>
       <c r="F12">
-        <v>130.49</v>
+        <v>143.539</v>
       </c>
       <c r="G12">
         <v>16.2</v>
@@ -2265,45 +2265,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M12">
-        <v>6.759382</v>
+        <v>7.679336500000001</v>
       </c>
       <c r="N12">
-        <v>64.54061800000001</v>
+        <v>63.62066350000001</v>
       </c>
       <c r="O12">
-        <v>14.52163905</v>
+        <v>14.3146492875</v>
       </c>
       <c r="P12">
-        <v>50.01897895</v>
+        <v>49.30601421250001</v>
       </c>
       <c r="Q12">
-        <v>75.21897895000001</v>
+        <v>74.50601421250001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1855190083621684</v>
+        <v>0.1867636674785876</v>
       </c>
       <c r="T12">
-        <v>0.9741827596252862</v>
+        <v>0.9828610738148846</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.225</v>
       </c>
       <c r="W12">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.54830160508757</v>
+        <v>9.284656298105963</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.170780539055943</v>
+        <v>0.1704477205859344</v>
       </c>
       <c r="C13">
-        <v>1294.382735532609</v>
+        <v>1285.129835858981</v>
       </c>
       <c r="D13">
-        <v>1421.721735532609</v>
+        <v>1425.517835858981</v>
       </c>
       <c r="E13">
-        <v>-381.6610000000001</v>
+        <v>-368.6120000000001</v>
       </c>
       <c r="F13">
-        <v>143.539</v>
+        <v>156.588</v>
       </c>
       <c r="G13">
         <v>16.2</v>
@@ -2347,28 +2347,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M13">
-        <v>7.679336500000001</v>
+        <v>8.377457999999999</v>
       </c>
       <c r="N13">
-        <v>63.62066350000001</v>
+        <v>62.92254200000001</v>
       </c>
       <c r="O13">
-        <v>14.3146492875</v>
+        <v>14.15757195</v>
       </c>
       <c r="P13">
-        <v>49.30601421250001</v>
+        <v>48.76497005000001</v>
       </c>
       <c r="Q13">
-        <v>74.50601421250001</v>
+        <v>73.96497005000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1867636674785876</v>
+        <v>0.1880366143021982</v>
       </c>
       <c r="T13">
-        <v>0.9828610738148846</v>
+        <v>0.9917366224178833</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.284656298105963</v>
+        <v>8.510934939930468</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1704477205859344</v>
+        <v>0.1701149021159259</v>
       </c>
       <c r="C14">
-        <v>1285.129835858981</v>
+        <v>1275.897262184588</v>
       </c>
       <c r="D14">
-        <v>1425.517835858981</v>
+        <v>1429.334262184588</v>
       </c>
       <c r="E14">
-        <v>-368.6120000000001</v>
+        <v>-355.563</v>
       </c>
       <c r="F14">
-        <v>156.588</v>
+        <v>169.637</v>
       </c>
       <c r="G14">
         <v>16.2</v>
@@ -2429,28 +2429,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M14">
-        <v>8.377457999999999</v>
+        <v>9.075579500000002</v>
       </c>
       <c r="N14">
-        <v>62.92254200000001</v>
+        <v>62.22442050000001</v>
       </c>
       <c r="O14">
-        <v>14.15757195</v>
+        <v>14.0004946125</v>
       </c>
       <c r="P14">
-        <v>48.76497005000001</v>
+        <v>48.2239258875</v>
       </c>
       <c r="Q14">
-        <v>73.96497005000001</v>
+        <v>73.42392588749999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1880366143021982</v>
+        <v>0.1893388242711792</v>
       </c>
       <c r="T14">
-        <v>0.9917366224178833</v>
+        <v>1.000816206620951</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.510934939930468</v>
+        <v>7.856247636858891</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1701149021159259</v>
+        <v>0.1698688836459173</v>
       </c>
       <c r="C15">
-        <v>1275.897262184588</v>
+        <v>1265.682515367015</v>
       </c>
       <c r="D15">
-        <v>1429.334262184588</v>
+        <v>1432.168515367015</v>
       </c>
       <c r="E15">
-        <v>-355.563</v>
+        <v>-342.514</v>
       </c>
       <c r="F15">
-        <v>169.637</v>
+        <v>182.686</v>
       </c>
       <c r="G15">
         <v>16.2</v>
@@ -2511,45 +2511,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M15">
-        <v>9.075579500000002</v>
+        <v>9.919849800000001</v>
       </c>
       <c r="N15">
-        <v>62.22442050000001</v>
+        <v>61.38015020000001</v>
       </c>
       <c r="O15">
-        <v>14.0004946125</v>
+        <v>13.810533795</v>
       </c>
       <c r="P15">
-        <v>48.2239258875</v>
+        <v>47.569616405</v>
       </c>
       <c r="Q15">
-        <v>73.42392588749999</v>
+        <v>72.76961640499999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1893388242711792</v>
+        <v>0.190671318192927</v>
       </c>
       <c r="T15">
-        <v>1.000816206620951</v>
+        <v>1.01010694394502</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.225</v>
       </c>
       <c r="W15">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.856247636858891</v>
+        <v>7.187608828512706</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1698688836459173</v>
+        <v>0.1695422651759087</v>
       </c>
       <c r="C16">
-        <v>1265.682515367015</v>
+        <v>1256.413732971878</v>
       </c>
       <c r="D16">
-        <v>1432.168515367015</v>
+        <v>1435.948732971878</v>
       </c>
       <c r="E16">
-        <v>-342.514</v>
+        <v>-329.465</v>
       </c>
       <c r="F16">
-        <v>182.686</v>
+        <v>195.735</v>
       </c>
       <c r="G16">
         <v>16.2</v>
@@ -2593,28 +2593,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M16">
-        <v>9.919849800000001</v>
+        <v>10.6284105</v>
       </c>
       <c r="N16">
-        <v>61.38015020000001</v>
+        <v>60.67158950000001</v>
       </c>
       <c r="O16">
-        <v>13.810533795</v>
+        <v>13.6511076375</v>
       </c>
       <c r="P16">
-        <v>47.569616405</v>
+        <v>47.02048186250001</v>
       </c>
       <c r="Q16">
-        <v>72.76961640499999</v>
+        <v>72.22048186250001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.190671318192927</v>
+        <v>0.1920351649128337</v>
       </c>
       <c r="T16">
-        <v>1.01010694394502</v>
+        <v>1.019616286853184</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.187608828512706</v>
+        <v>6.708434906611858</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1695422651759087</v>
+        <v>0.1692156467059001</v>
       </c>
       <c r="C17">
-        <v>1256.413732971878</v>
+        <v>1247.164959204875</v>
       </c>
       <c r="D17">
-        <v>1435.948732971878</v>
+        <v>1439.748959204875</v>
       </c>
       <c r="E17">
-        <v>-329.465</v>
+        <v>-316.4160000000001</v>
       </c>
       <c r="F17">
-        <v>195.735</v>
+        <v>208.784</v>
       </c>
       <c r="G17">
         <v>16.2</v>
@@ -2675,28 +2675,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M17">
-        <v>10.6284105</v>
+        <v>11.3369712</v>
       </c>
       <c r="N17">
-        <v>60.67158950000001</v>
+        <v>59.96302880000001</v>
       </c>
       <c r="O17">
-        <v>13.6511076375</v>
+        <v>13.49168148</v>
       </c>
       <c r="P17">
-        <v>47.02048186250001</v>
+        <v>46.47134732000001</v>
       </c>
       <c r="Q17">
-        <v>72.22048186250001</v>
+        <v>71.67134732</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1920351649128337</v>
+        <v>0.1934314841736906</v>
       </c>
       <c r="T17">
-        <v>1.019616286853184</v>
+        <v>1.029352042687734</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.708434906611859</v>
+        <v>6.289157724948618</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1692156467059001</v>
+        <v>0.1690207782358915</v>
       </c>
       <c r="C18">
-        <v>1247.164959204875</v>
+        <v>1236.392861533309</v>
       </c>
       <c r="D18">
-        <v>1439.748959204875</v>
+        <v>1442.025861533309</v>
       </c>
       <c r="E18">
-        <v>-316.4160000000001</v>
+        <v>-303.367</v>
       </c>
       <c r="F18">
-        <v>208.784</v>
+        <v>221.833</v>
       </c>
       <c r="G18">
         <v>16.2</v>
@@ -2757,45 +2757,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M18">
-        <v>11.3369712</v>
+        <v>12.2673649</v>
       </c>
       <c r="N18">
-        <v>59.96302880000001</v>
+        <v>59.03263510000001</v>
       </c>
       <c r="O18">
-        <v>13.49168148</v>
+        <v>13.2823428975</v>
       </c>
       <c r="P18">
-        <v>46.47134732000001</v>
+        <v>45.75029220250001</v>
       </c>
       <c r="Q18">
-        <v>71.67134732</v>
+        <v>70.95029220250001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1934314841736906</v>
+        <v>0.194861449681797</v>
       </c>
       <c r="T18">
-        <v>1.029352042687734</v>
+        <v>1.039322395048417</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.225</v>
       </c>
       <c r="W18">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.289157724948618</v>
+        <v>5.812169164381831</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1690207782358915</v>
+        <v>0.1687019097658829</v>
       </c>
       <c r="C19">
-        <v>1236.392861533309</v>
+        <v>1227.085191355244</v>
       </c>
       <c r="D19">
-        <v>1442.025861533309</v>
+        <v>1445.767191355244</v>
       </c>
       <c r="E19">
-        <v>-303.367</v>
+        <v>-290.318</v>
       </c>
       <c r="F19">
-        <v>221.833</v>
+        <v>234.882</v>
       </c>
       <c r="G19">
         <v>16.2</v>
@@ -2839,28 +2839,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M19">
-        <v>12.2673649</v>
+        <v>12.9889746</v>
       </c>
       <c r="N19">
-        <v>59.03263510000001</v>
+        <v>58.31102540000001</v>
       </c>
       <c r="O19">
-        <v>13.2823428975</v>
+        <v>13.119980715</v>
       </c>
       <c r="P19">
-        <v>45.75029220250001</v>
+        <v>45.191044685</v>
       </c>
       <c r="Q19">
-        <v>70.95029220250001</v>
+        <v>70.391044685</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.194861449681797</v>
+        <v>0.1963262923974182</v>
       </c>
       <c r="T19">
-        <v>1.039322395048417</v>
+        <v>1.049535926734971</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.812169164381831</v>
+        <v>5.489270877471728</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.168701909765883</v>
+        <v>0.1683830412958743</v>
       </c>
       <c r="C20">
-        <v>1227.085191355244</v>
+        <v>1217.796985404915</v>
       </c>
       <c r="D20">
-        <v>1445.767191355244</v>
+        <v>1449.527985404915</v>
       </c>
       <c r="E20">
-        <v>-290.318</v>
+        <v>-277.269</v>
       </c>
       <c r="F20">
-        <v>234.882</v>
+        <v>247.931</v>
       </c>
       <c r="G20">
         <v>16.2</v>
@@ -2921,28 +2921,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M20">
-        <v>12.9889746</v>
+        <v>13.7105843</v>
       </c>
       <c r="N20">
-        <v>58.31102540000001</v>
+        <v>57.58941570000001</v>
       </c>
       <c r="O20">
-        <v>13.119980715</v>
+        <v>12.9576185325</v>
       </c>
       <c r="P20">
-        <v>45.19104468500001</v>
+        <v>44.63179716750001</v>
       </c>
       <c r="Q20">
-        <v>70.391044685</v>
+        <v>69.83179716750001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1963262923974182</v>
+        <v>0.1978273040689806</v>
       </c>
       <c r="T20">
-        <v>1.049535926734971</v>
+        <v>1.060001644389094</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.489270877471729</v>
+        <v>5.200361883920586</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1683830412958743</v>
+        <v>0.1680641728258658</v>
       </c>
       <c r="C21">
-        <v>1217.796985404915</v>
+        <v>1208.528395972113</v>
       </c>
       <c r="D21">
-        <v>1449.527985404915</v>
+        <v>1453.308395972113</v>
       </c>
       <c r="E21">
-        <v>-277.269</v>
+        <v>-264.22</v>
       </c>
       <c r="F21">
-        <v>247.931</v>
+        <v>260.98</v>
       </c>
       <c r="G21">
         <v>16.2</v>
@@ -3003,28 +3003,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M21">
-        <v>13.7105843</v>
+        <v>14.432194</v>
       </c>
       <c r="N21">
-        <v>57.58941570000001</v>
+        <v>56.86780600000001</v>
       </c>
       <c r="O21">
-        <v>12.9576185325</v>
+        <v>12.79525635</v>
       </c>
       <c r="P21">
-        <v>44.63179716750001</v>
+        <v>44.07254965000001</v>
       </c>
       <c r="Q21">
-        <v>69.83179716750001</v>
+        <v>69.27254965</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1978273040689806</v>
+        <v>0.1993658410323322</v>
       </c>
       <c r="T21">
-        <v>1.060001644389094</v>
+        <v>1.07072900498457</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.200361883920586</v>
+        <v>4.940343789724556</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1680641728258658</v>
+        <v>0.1677453043558572</v>
       </c>
       <c r="C22">
-        <v>1208.528395972113</v>
+        <v>1199.279576939492</v>
       </c>
       <c r="D22">
-        <v>1453.308395972113</v>
+        <v>1457.108576939492</v>
       </c>
       <c r="E22">
-        <v>-264.22</v>
+        <v>-251.171</v>
       </c>
       <c r="F22">
-        <v>260.98</v>
+        <v>274.0290000000001</v>
       </c>
       <c r="G22">
         <v>16.2</v>
@@ -3085,28 +3085,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M22">
-        <v>14.432194</v>
+        <v>15.1538037</v>
       </c>
       <c r="N22">
-        <v>56.86780600000001</v>
+        <v>56.14619630000001</v>
       </c>
       <c r="O22">
-        <v>12.79525635</v>
+        <v>12.6328941675</v>
       </c>
       <c r="P22">
-        <v>44.07254965000001</v>
+        <v>43.5133021325</v>
       </c>
       <c r="Q22">
-        <v>69.27254965</v>
+        <v>68.71330213249999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1993658410323322</v>
+        <v>0.2009433282985534</v>
       </c>
       <c r="T22">
-        <v>1.07072900498457</v>
+        <v>1.081727944329298</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.940343789724556</v>
+        <v>4.705089323547196</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1677453043558572</v>
+        <v>0.1678526858858486</v>
       </c>
       <c r="C23">
-        <v>1199.279576939492</v>
+        <v>1184.948617864033</v>
       </c>
       <c r="D23">
-        <v>1457.108576939492</v>
+        <v>1455.826617864033</v>
       </c>
       <c r="E23">
-        <v>-251.171</v>
+        <v>-238.122</v>
       </c>
       <c r="F23">
-        <v>274.029</v>
+        <v>287.078</v>
       </c>
       <c r="G23">
         <v>16.2</v>
@@ -3167,45 +3167,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M23">
-        <v>15.1538037</v>
+        <v>16.5931084</v>
       </c>
       <c r="N23">
-        <v>56.14619630000001</v>
+        <v>54.70689160000001</v>
       </c>
       <c r="O23">
-        <v>12.6328941675</v>
+        <v>12.30905061</v>
       </c>
       <c r="P23">
-        <v>43.51330213250001</v>
+        <v>42.39784099000001</v>
       </c>
       <c r="Q23">
-        <v>68.7133021325</v>
+        <v>67.59784099000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2009433282985534</v>
+        <v>0.2025612639562162</v>
       </c>
       <c r="T23">
-        <v>1.081727944329298</v>
+        <v>1.093008907759789</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.225</v>
       </c>
       <c r="W23">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.705089323547197</v>
+        <v>4.296964636234161</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1678526858858486</v>
+        <v>0.16755319241584</v>
       </c>
       <c r="C24">
-        <v>1184.948617864033</v>
+        <v>1175.480719573677</v>
       </c>
       <c r="D24">
-        <v>1455.826617864033</v>
+        <v>1459.407719573677</v>
       </c>
       <c r="E24">
-        <v>-238.122</v>
+        <v>-225.073</v>
       </c>
       <c r="F24">
-        <v>287.078</v>
+        <v>300.127</v>
       </c>
       <c r="G24">
         <v>16.2</v>
@@ -3249,28 +3249,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M24">
-        <v>16.5931084</v>
+        <v>17.3473406</v>
       </c>
       <c r="N24">
-        <v>54.70689160000001</v>
+        <v>53.95265940000001</v>
       </c>
       <c r="O24">
-        <v>12.30905061</v>
+        <v>12.139348365</v>
       </c>
       <c r="P24">
-        <v>42.39784099000001</v>
+        <v>41.81331103500001</v>
       </c>
       <c r="Q24">
-        <v>67.59784099000001</v>
+        <v>67.013311035</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2025612639562162</v>
+        <v>0.2042212239166753</v>
       </c>
       <c r="T24">
-        <v>1.093008907759789</v>
+        <v>1.104582883227435</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.296964636234161</v>
+        <v>4.110140086832676</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.16755319241584</v>
+        <v>0.1679046989458314</v>
       </c>
       <c r="C25">
-        <v>1175.480719573677</v>
+        <v>1158.230477952521</v>
       </c>
       <c r="D25">
-        <v>1459.407719573677</v>
+        <v>1455.206477952521</v>
       </c>
       <c r="E25">
-        <v>-225.073</v>
+        <v>-212.024</v>
       </c>
       <c r="F25">
-        <v>300.127</v>
+        <v>313.176</v>
       </c>
       <c r="G25">
         <v>16.2</v>
@@ -3331,45 +3331,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M25">
-        <v>17.3473406</v>
+        <v>19.1976888</v>
       </c>
       <c r="N25">
-        <v>53.95265940000001</v>
+        <v>52.10231120000001</v>
       </c>
       <c r="O25">
-        <v>12.139348365</v>
+        <v>11.72302002</v>
       </c>
       <c r="P25">
-        <v>41.81331103500001</v>
+        <v>40.37929118000001</v>
       </c>
       <c r="Q25">
-        <v>67.013311035</v>
+        <v>65.57929118000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2042212239166753</v>
+        <v>0.2059248670339887</v>
       </c>
       <c r="T25">
-        <v>1.104582883227435</v>
+        <v>1.116461436996862</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.225</v>
       </c>
       <c r="W25">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.110140086832676</v>
+        <v>3.713988738061011</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1679046989458314</v>
+        <v>0.1676323304758228</v>
       </c>
       <c r="C26">
-        <v>1158.230477952521</v>
+        <v>1148.434738892359</v>
       </c>
       <c r="D26">
-        <v>1455.206477952521</v>
+        <v>1458.459738892359</v>
       </c>
       <c r="E26">
-        <v>-212.0240000000001</v>
+        <v>-198.975</v>
       </c>
       <c r="F26">
-        <v>313.176</v>
+        <v>326.225</v>
       </c>
       <c r="G26">
         <v>16.2</v>
@@ -3413,28 +3413,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M26">
-        <v>19.1976888</v>
+        <v>19.9975925</v>
       </c>
       <c r="N26">
-        <v>52.10231120000002</v>
+        <v>51.30240750000001</v>
       </c>
       <c r="O26">
-        <v>11.72302002</v>
+        <v>11.5430416875</v>
       </c>
       <c r="P26">
-        <v>40.37929118000001</v>
+        <v>39.75936581250001</v>
       </c>
       <c r="Q26">
-        <v>65.57929118000001</v>
+        <v>64.95936581250001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2059248670339887</v>
+        <v>0.2076739406344305</v>
       </c>
       <c r="T26">
-        <v>1.116461436996862</v>
+        <v>1.12865675220014</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.713988738061012</v>
+        <v>3.56542918853857</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1676323304758228</v>
+        <v>0.1679241620058142</v>
       </c>
       <c r="C27">
-        <v>1148.434738892359</v>
+        <v>1131.900560119861</v>
       </c>
       <c r="D27">
-        <v>1458.459738892359</v>
+        <v>1454.974560119861</v>
       </c>
       <c r="E27">
-        <v>-198.975</v>
+        <v>-185.926</v>
       </c>
       <c r="F27">
-        <v>326.225</v>
+        <v>339.2740000000001</v>
       </c>
       <c r="G27">
         <v>16.2</v>
@@ -3495,45 +3495,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M27">
-        <v>19.9975925</v>
+        <v>21.7474634</v>
       </c>
       <c r="N27">
-        <v>51.30240750000001</v>
+        <v>49.55253660000001</v>
       </c>
       <c r="O27">
-        <v>11.5430416875</v>
+        <v>11.149320735</v>
       </c>
       <c r="P27">
-        <v>39.75936581250001</v>
+        <v>38.40321586500001</v>
       </c>
       <c r="Q27">
-        <v>64.95936581250001</v>
+        <v>63.603215865</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2076739406344305</v>
+        <v>0.2094702864943436</v>
       </c>
       <c r="T27">
-        <v>1.12865675220014</v>
+        <v>1.14118167051702</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.225</v>
       </c>
       <c r="W27">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.56542918853857</v>
+        <v>3.278543280592439</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1679241620058142</v>
+        <v>0.1676734935358057</v>
       </c>
       <c r="C28">
-        <v>1131.900560119861</v>
+        <v>1121.844140674545</v>
       </c>
       <c r="D28">
-        <v>1454.974560119861</v>
+        <v>1457.967140674545</v>
       </c>
       <c r="E28">
-        <v>-185.926</v>
+        <v>-172.877</v>
       </c>
       <c r="F28">
-        <v>339.2740000000001</v>
+        <v>352.323</v>
       </c>
       <c r="G28">
         <v>16.2</v>
@@ -3577,28 +3577,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M28">
-        <v>21.7474634</v>
+        <v>22.5839043</v>
       </c>
       <c r="N28">
-        <v>49.55253660000001</v>
+        <v>48.71609570000001</v>
       </c>
       <c r="O28">
-        <v>11.149320735</v>
+        <v>10.9611215325</v>
       </c>
       <c r="P28">
-        <v>38.40321586500001</v>
+        <v>37.75497416750001</v>
       </c>
       <c r="Q28">
-        <v>63.603215865</v>
+        <v>62.9549741675</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2094702864943436</v>
+        <v>0.2113158473093228</v>
       </c>
       <c r="T28">
-        <v>1.14118167051702</v>
+        <v>1.154049737280938</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.278543280592439</v>
+        <v>3.157115751681608</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1676734935358057</v>
+        <v>0.1674228250657971</v>
       </c>
       <c r="C29">
-        <v>1121.844140674545</v>
+        <v>1111.800056834632</v>
       </c>
       <c r="D29">
-        <v>1457.967140674545</v>
+        <v>1460.972056834632</v>
       </c>
       <c r="E29">
-        <v>-172.877</v>
+        <v>-159.828</v>
       </c>
       <c r="F29">
-        <v>352.323</v>
+        <v>365.3720000000001</v>
       </c>
       <c r="G29">
         <v>16.2</v>
@@ -3659,28 +3659,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M29">
-        <v>22.5839043</v>
+        <v>23.42034520000001</v>
       </c>
       <c r="N29">
-        <v>48.71609570000001</v>
+        <v>47.8796548</v>
       </c>
       <c r="O29">
-        <v>10.9611215325</v>
+        <v>10.77292233</v>
       </c>
       <c r="P29">
-        <v>37.75497416750001</v>
+        <v>37.10673247</v>
       </c>
       <c r="Q29">
-        <v>62.9549741675</v>
+        <v>62.30673247</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2113158473093228</v>
+        <v>0.2132126737024959</v>
       </c>
       <c r="T29">
-        <v>1.154049737280938</v>
+        <v>1.167275250343853</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.157115751681608</v>
+        <v>3.044361617692979</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1674228250657971</v>
+        <v>0.1689252065957885</v>
       </c>
       <c r="C30">
-        <v>1111.800056834632</v>
+        <v>1080.924183729535</v>
       </c>
       <c r="D30">
-        <v>1460.972056834632</v>
+        <v>1443.145183729535</v>
       </c>
       <c r="E30">
-        <v>-159.828</v>
+        <v>-146.779</v>
       </c>
       <c r="F30">
-        <v>365.3720000000001</v>
+        <v>378.421</v>
       </c>
       <c r="G30">
         <v>16.2</v>
@@ -3741,45 +3741,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M30">
-        <v>23.42034520000001</v>
+        <v>27.2084699</v>
       </c>
       <c r="N30">
-        <v>47.8796548</v>
+        <v>44.09153010000001</v>
       </c>
       <c r="O30">
-        <v>10.77292233</v>
+        <v>9.920594272500002</v>
       </c>
       <c r="P30">
-        <v>37.10673247</v>
+        <v>34.1709358275</v>
       </c>
       <c r="Q30">
-        <v>62.30673247</v>
+        <v>59.3709358275</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2132126737024959</v>
+        <v>0.2151629318250542</v>
       </c>
       <c r="T30">
-        <v>1.167275250343853</v>
+        <v>1.180873313070513</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.225</v>
       </c>
       <c r="W30">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.044361617692979</v>
+        <v>2.620507520711409</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1689252065957885</v>
+        <v>0.1687349881257799</v>
       </c>
       <c r="C31">
-        <v>1080.924183729536</v>
+        <v>1070.108175923494</v>
       </c>
       <c r="D31">
-        <v>1443.145183729536</v>
+        <v>1445.378175923494</v>
       </c>
       <c r="E31">
-        <v>-146.7790000000001</v>
+        <v>-133.73</v>
       </c>
       <c r="F31">
-        <v>378.421</v>
+        <v>391.47</v>
       </c>
       <c r="G31">
         <v>16.2</v>
@@ -3823,28 +3823,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M31">
-        <v>27.2084699</v>
+        <v>28.146693</v>
       </c>
       <c r="N31">
-        <v>44.09153010000001</v>
+        <v>43.15330700000001</v>
       </c>
       <c r="O31">
-        <v>9.920594272500004</v>
+        <v>9.709494075000004</v>
       </c>
       <c r="P31">
-        <v>34.17093582750001</v>
+        <v>33.44381292500001</v>
       </c>
       <c r="Q31">
-        <v>59.37093582750001</v>
+        <v>58.64381292500001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2151629318250542</v>
+        <v>0.217168911608257</v>
       </c>
       <c r="T31">
-        <v>1.180873313070513</v>
+        <v>1.194859891875077</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.620507520711409</v>
+        <v>2.533157270021029</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1687349881257799</v>
+        <v>0.1694817446557713</v>
       </c>
       <c r="C32">
-        <v>1070.108175923494</v>
+        <v>1048.332378010173</v>
       </c>
       <c r="D32">
-        <v>1445.378175923494</v>
+        <v>1436.651378010173</v>
       </c>
       <c r="E32">
-        <v>-133.73</v>
+        <v>-120.681</v>
       </c>
       <c r="F32">
-        <v>391.47</v>
+        <v>404.519</v>
       </c>
       <c r="G32">
         <v>16.2</v>
@@ -3905,45 +3905,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M32">
-        <v>28.146693</v>
+        <v>30.6625402</v>
       </c>
       <c r="N32">
-        <v>43.15330700000001</v>
+        <v>40.63745980000001</v>
       </c>
       <c r="O32">
-        <v>9.709494075000004</v>
+        <v>9.143428455000002</v>
       </c>
       <c r="P32">
-        <v>33.44381292500001</v>
+        <v>31.49403134500001</v>
       </c>
       <c r="Q32">
-        <v>58.64381292500001</v>
+        <v>56.694031345</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.217168911608257</v>
+        <v>0.2192330357330019</v>
       </c>
       <c r="T32">
-        <v>1.194859891875077</v>
+        <v>1.209251878760933</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.225</v>
       </c>
       <c r="W32">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.533157270021029</v>
+        <v>2.325312891069606</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1694817446557713</v>
+        <v>0.1693217511857627</v>
       </c>
       <c r="C33">
-        <v>1048.332378010173</v>
+        <v>1037.144223059357</v>
       </c>
       <c r="D33">
-        <v>1436.651378010173</v>
+        <v>1438.512223059357</v>
       </c>
       <c r="E33">
-        <v>-120.681</v>
+        <v>-107.632</v>
       </c>
       <c r="F33">
-        <v>404.519</v>
+        <v>417.568</v>
       </c>
       <c r="G33">
         <v>16.2</v>
@@ -3987,28 +3987,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M33">
-        <v>30.6625402</v>
+        <v>31.65165440000001</v>
       </c>
       <c r="N33">
-        <v>40.63745980000001</v>
+        <v>39.64834560000001</v>
       </c>
       <c r="O33">
-        <v>9.143428455000002</v>
+        <v>8.920877760000002</v>
       </c>
       <c r="P33">
-        <v>31.49403134500001</v>
+        <v>30.72746784</v>
       </c>
       <c r="Q33">
-        <v>56.694031345</v>
+        <v>55.92746784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2192330357330019</v>
+        <v>0.2213578693908275</v>
       </c>
       <c r="T33">
-        <v>1.209251878760933</v>
+        <v>1.224067159378726</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.325312891069606</v>
+        <v>2.25264686322368</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1693217511857627</v>
+        <v>0.1691617577157542</v>
       </c>
       <c r="C34">
-        <v>1037.144223059357</v>
+        <v>1025.960894937567</v>
       </c>
       <c r="D34">
-        <v>1438.512223059357</v>
+        <v>1440.377894937568</v>
       </c>
       <c r="E34">
-        <v>-107.632</v>
+        <v>-94.58299999999997</v>
       </c>
       <c r="F34">
-        <v>417.568</v>
+        <v>430.6170000000001</v>
       </c>
       <c r="G34">
         <v>16.2</v>
@@ -4069,28 +4069,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M34">
-        <v>31.65165440000001</v>
+        <v>32.64076860000001</v>
       </c>
       <c r="N34">
-        <v>39.64834560000001</v>
+        <v>38.6592314</v>
       </c>
       <c r="O34">
-        <v>8.920877760000002</v>
+        <v>8.698327065000001</v>
       </c>
       <c r="P34">
-        <v>30.72746784</v>
+        <v>29.960904335</v>
       </c>
       <c r="Q34">
-        <v>55.92746784</v>
+        <v>55.160904335</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2213578693908275</v>
+        <v>0.2235461309190361</v>
       </c>
       <c r="T34">
-        <v>1.224067159378726</v>
+        <v>1.23932468717914</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.25264686322368</v>
+        <v>2.184384837065387</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1691617577157542</v>
+        <v>0.1690017642457456</v>
       </c>
       <c r="C35">
-        <v>1025.960894937567</v>
+        <v>1014.782412449598</v>
       </c>
       <c r="D35">
-        <v>1440.377894937568</v>
+        <v>1442.248412449598</v>
       </c>
       <c r="E35">
-        <v>-94.58299999999997</v>
+        <v>-81.53399999999999</v>
       </c>
       <c r="F35">
-        <v>430.6170000000001</v>
+        <v>443.6660000000001</v>
       </c>
       <c r="G35">
         <v>16.2</v>
@@ -4151,28 +4151,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M35">
-        <v>32.64076860000001</v>
+        <v>33.6298828</v>
       </c>
       <c r="N35">
-        <v>38.6592314</v>
+        <v>37.67011720000001</v>
       </c>
       <c r="O35">
-        <v>8.698327065000001</v>
+        <v>8.475776370000002</v>
       </c>
       <c r="P35">
-        <v>29.960904335</v>
+        <v>29.19434083000001</v>
       </c>
       <c r="Q35">
-        <v>55.160904335</v>
+        <v>54.39434083</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2235461309190361</v>
+        <v>0.2258007034026448</v>
       </c>
       <c r="T35">
-        <v>1.23932468717914</v>
+        <v>1.255044564306838</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.184384837065387</v>
+        <v>2.120138224210523</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1690017642457456</v>
+        <v>0.168841770775737</v>
       </c>
       <c r="C36">
-        <v>1014.782412449598</v>
+        <v>1003.608794498047</v>
       </c>
       <c r="D36">
-        <v>1442.248412449598</v>
+        <v>1444.123794498047</v>
       </c>
       <c r="E36">
-        <v>-81.53399999999999</v>
+        <v>-68.48499999999996</v>
       </c>
       <c r="F36">
-        <v>443.6660000000001</v>
+        <v>456.7150000000001</v>
       </c>
       <c r="G36">
         <v>16.2</v>
@@ -4233,28 +4233,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M36">
-        <v>33.6298828</v>
+        <v>34.61899700000001</v>
       </c>
       <c r="N36">
-        <v>37.67011720000001</v>
+        <v>36.681003</v>
       </c>
       <c r="O36">
-        <v>8.475776370000002</v>
+        <v>8.253225675000001</v>
       </c>
       <c r="P36">
-        <v>29.19434083000001</v>
+        <v>28.427777325</v>
       </c>
       <c r="Q36">
-        <v>54.39434083</v>
+        <v>53.627777325</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2258007034026448</v>
+        <v>0.2281246473472877</v>
       </c>
       <c r="T36">
-        <v>1.255044564306838</v>
+        <v>1.271248129961543</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.120138224210523</v>
+        <v>2.059562846375936</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.168841770775737</v>
+        <v>0.1686817773057284</v>
       </c>
       <c r="C37">
-        <v>1003.608794498047</v>
+        <v>992.4400600839597</v>
       </c>
       <c r="D37">
-        <v>1444.123794498047</v>
+        <v>1446.00406008396</v>
       </c>
       <c r="E37">
-        <v>-68.48499999999996</v>
+        <v>-55.43599999999998</v>
       </c>
       <c r="F37">
-        <v>456.7150000000001</v>
+        <v>469.7640000000001</v>
       </c>
       <c r="G37">
         <v>16.2</v>
@@ -4315,28 +4315,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M37">
-        <v>34.61899700000001</v>
+        <v>35.60811120000001</v>
       </c>
       <c r="N37">
-        <v>36.681003</v>
+        <v>35.6918888</v>
       </c>
       <c r="O37">
-        <v>8.253225675000001</v>
+        <v>8.030674980000001</v>
       </c>
       <c r="P37">
-        <v>28.427777325</v>
+        <v>27.66121382</v>
       </c>
       <c r="Q37">
-        <v>53.627777325</v>
+        <v>52.86121382</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2281246473472877</v>
+        <v>0.2305212145402006</v>
       </c>
       <c r="T37">
-        <v>1.271248129961543</v>
+        <v>1.287958057042958</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.059562846375936</v>
+        <v>2.002352767309937</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1686817773057284</v>
+        <v>0.1725936338357199</v>
       </c>
       <c r="C38">
-        <v>992.4400600839593</v>
+        <v>934.778722273983</v>
       </c>
       <c r="D38">
-        <v>1446.004060083959</v>
+        <v>1401.391722273983</v>
       </c>
       <c r="E38">
-        <v>-55.43600000000004</v>
+        <v>-42.387</v>
       </c>
       <c r="F38">
-        <v>469.764</v>
+        <v>482.813</v>
       </c>
       <c r="G38">
         <v>16.2</v>
@@ -4397,45 +4397,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M38">
-        <v>35.6081112</v>
+        <v>43.45317</v>
       </c>
       <c r="N38">
-        <v>35.69188880000001</v>
+        <v>27.84683000000001</v>
       </c>
       <c r="O38">
-        <v>8.030674980000002</v>
+        <v>6.265536750000003</v>
       </c>
       <c r="P38">
-        <v>27.66121382000001</v>
+        <v>21.58129325000001</v>
       </c>
       <c r="Q38">
-        <v>52.86121382</v>
+        <v>46.78129325</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2305212145402006</v>
+        <v>0.2329938632313013</v>
       </c>
       <c r="T38">
-        <v>1.287958057042958</v>
+        <v>1.305198457999973</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.225</v>
       </c>
       <c r="W38">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.002352767309938</v>
+        <v>1.640846916346955</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1725936338357199</v>
+        <v>0.1725436903657112</v>
       </c>
       <c r="C39">
-        <v>934.778722273983</v>
+        <v>922.2819419959258</v>
       </c>
       <c r="D39">
-        <v>1401.391722273983</v>
+        <v>1401.943941995926</v>
       </c>
       <c r="E39">
-        <v>-42.387</v>
+        <v>-29.33800000000002</v>
       </c>
       <c r="F39">
-        <v>482.813</v>
+        <v>495.862</v>
       </c>
       <c r="G39">
         <v>16.2</v>
@@ -4479,28 +4479,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M39">
-        <v>43.45317</v>
+        <v>44.62758</v>
       </c>
       <c r="N39">
-        <v>27.84683000000001</v>
+        <v>26.67242000000001</v>
       </c>
       <c r="O39">
-        <v>6.265536750000003</v>
+        <v>6.001294500000002</v>
       </c>
       <c r="P39">
-        <v>21.58129325000001</v>
+        <v>20.67112550000001</v>
       </c>
       <c r="Q39">
-        <v>46.78129325</v>
+        <v>45.87112550000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2329938632313013</v>
+        <v>0.2355462747834052</v>
       </c>
       <c r="T39">
-        <v>1.305198457999973</v>
+        <v>1.322995000923343</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.640846916346955</v>
+        <v>1.597666734337825</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1725436903657112</v>
+        <v>0.1724937468957026</v>
       </c>
       <c r="C40">
-        <v>922.2819419959258</v>
+        <v>909.7855970948269</v>
       </c>
       <c r="D40">
-        <v>1401.943941995926</v>
+        <v>1402.496597094827</v>
       </c>
       <c r="E40">
-        <v>-29.33800000000002</v>
+        <v>-16.28899999999999</v>
       </c>
       <c r="F40">
-        <v>495.862</v>
+        <v>508.9110000000001</v>
       </c>
       <c r="G40">
         <v>16.2</v>
@@ -4561,28 +4561,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M40">
-        <v>44.62758</v>
+        <v>45.80199</v>
       </c>
       <c r="N40">
-        <v>26.67242000000001</v>
+        <v>25.49801000000001</v>
       </c>
       <c r="O40">
-        <v>6.001294500000002</v>
+        <v>5.737052250000002</v>
       </c>
       <c r="P40">
-        <v>20.67112550000001</v>
+        <v>19.76095775000001</v>
       </c>
       <c r="Q40">
-        <v>45.87112550000001</v>
+        <v>44.96095775000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2355462747834052</v>
+        <v>0.2381823719601683</v>
       </c>
       <c r="T40">
-        <v>1.322995000923343</v>
+        <v>1.341375037057315</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.597666734337825</v>
+        <v>1.556700920636855</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1724937468957026</v>
+        <v>0.1724438034256941</v>
       </c>
       <c r="C41">
-        <v>909.7855970948269</v>
+        <v>897.2896880857747</v>
       </c>
       <c r="D41">
-        <v>1402.496597094827</v>
+        <v>1403.049688085775</v>
       </c>
       <c r="E41">
-        <v>-16.28899999999999</v>
+        <v>-3.240000000000009</v>
       </c>
       <c r="F41">
-        <v>508.9110000000001</v>
+        <v>521.96</v>
       </c>
       <c r="G41">
         <v>16.2</v>
@@ -4643,28 +4643,28 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M41">
-        <v>45.80199</v>
+        <v>46.9764</v>
       </c>
       <c r="N41">
-        <v>25.49801000000001</v>
+        <v>24.32360000000001</v>
       </c>
       <c r="O41">
-        <v>5.737052250000002</v>
+        <v>5.472810000000004</v>
       </c>
       <c r="P41">
-        <v>19.76095775000001</v>
+        <v>18.85079000000001</v>
       </c>
       <c r="Q41">
-        <v>44.96095775000001</v>
+        <v>44.05079000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2381823719601683</v>
+        <v>0.2409063390428234</v>
       </c>
       <c r="T41">
-        <v>1.341375037057315</v>
+        <v>1.36036774106242</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.556700920636855</v>
+        <v>1.517783397620933</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1724438034256941</v>
+        <v>0.192784165806236</v>
       </c>
       <c r="C42">
-        <v>897.2896880857747</v>
+        <v>690.0800522306698</v>
       </c>
       <c r="D42">
-        <v>1403.049688085775</v>
+        <v>1208.88905223067</v>
       </c>
       <c r="E42">
-        <v>-3.240000000000009</v>
+        <v>9.809000000000083</v>
       </c>
       <c r="F42">
-        <v>521.96</v>
+        <v>535.0090000000001</v>
       </c>
       <c r="G42">
         <v>16.2</v>
@@ -4725,45 +4725,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M42">
-        <v>46.9764</v>
+        <v>78.53932120000003</v>
       </c>
       <c r="N42">
-        <v>24.32360000000001</v>
+        <v>-7.23932120000002</v>
       </c>
       <c r="O42">
-        <v>5.472810000000004</v>
+        <v>-1.628847270000005</v>
       </c>
       <c r="P42">
-        <v>18.85079000000001</v>
+        <v>-5.610473930000015</v>
       </c>
       <c r="Q42">
-        <v>44.05079000000001</v>
+        <v>19.58952606999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2409063390428234</v>
+        <v>0.2455766293677382</v>
       </c>
       <c r="T42">
-        <v>1.36036774106242</v>
+        <v>1.392931072067342</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.225</v>
+        <v>0.2042607416882029</v>
       </c>
       <c r="W42">
-        <v>0.06974999999999999</v>
+        <v>0.1168145231201718</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.517783397620933</v>
+        <v>0.907825518614235</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.192784165806236</v>
+        <v>0.193794165806236</v>
       </c>
       <c r="C43">
-        <v>690.0800522306698</v>
+        <v>668.7808760422951</v>
       </c>
       <c r="D43">
-        <v>1208.88905223067</v>
+        <v>1200.638876042295</v>
       </c>
       <c r="E43">
-        <v>9.809000000000083</v>
+        <v>22.85800000000006</v>
       </c>
       <c r="F43">
-        <v>535.0090000000001</v>
+        <v>548.0580000000001</v>
       </c>
       <c r="G43">
         <v>16.2</v>
@@ -4807,37 +4807,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M43">
-        <v>78.53932120000003</v>
+        <v>80.45491440000002</v>
       </c>
       <c r="N43">
-        <v>-7.23932120000002</v>
+        <v>-9.15491440000001</v>
       </c>
       <c r="O43">
-        <v>-1.628847270000005</v>
+        <v>-2.059855740000002</v>
       </c>
       <c r="P43">
-        <v>-5.610473930000015</v>
+        <v>-7.095058660000007</v>
       </c>
       <c r="Q43">
-        <v>19.58952606999998</v>
+        <v>18.10494133999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2455766293677382</v>
+        <v>0.2490210540120095</v>
       </c>
       <c r="T43">
-        <v>1.392931072067342</v>
+        <v>1.41694712503402</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2042607416882029</v>
+        <v>0.1993973906956266</v>
       </c>
       <c r="W43">
-        <v>0.1168145231201718</v>
+        <v>0.117528463045882</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.907825518614235</v>
+        <v>0.8862106253138962</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.193794165806236</v>
+        <v>0.1948041658062359</v>
       </c>
       <c r="C44">
-        <v>668.7808760422952</v>
+        <v>647.5935447530907</v>
       </c>
       <c r="D44">
-        <v>1200.638876042295</v>
+        <v>1192.500544753091</v>
       </c>
       <c r="E44">
-        <v>22.85799999999995</v>
+        <v>35.90700000000004</v>
       </c>
       <c r="F44">
-        <v>548.058</v>
+        <v>561.1070000000001</v>
       </c>
       <c r="G44">
         <v>16.2</v>
@@ -4889,37 +4889,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M44">
-        <v>80.45491440000001</v>
+        <v>82.37050760000002</v>
       </c>
       <c r="N44">
-        <v>-9.154914399999996</v>
+        <v>-11.07050760000001</v>
       </c>
       <c r="O44">
-        <v>-2.059855739999999</v>
+        <v>-2.490864210000003</v>
       </c>
       <c r="P44">
-        <v>-7.095058659999996</v>
+        <v>-8.57964339000001</v>
       </c>
       <c r="Q44">
-        <v>18.10494134</v>
+        <v>16.62035660999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2490210540120095</v>
+        <v>0.252586335661343</v>
       </c>
       <c r="T44">
-        <v>1.41694712503402</v>
+        <v>1.441805846525845</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1993973906956267</v>
+        <v>0.1947602420747981</v>
       </c>
       <c r="W44">
-        <v>0.117528463045882</v>
+        <v>0.1182091964634196</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8862106253138964</v>
+        <v>0.8656010758879916</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1948041658062359</v>
+        <v>0.195814165806236</v>
       </c>
       <c r="C45">
-        <v>647.5935447530907</v>
+        <v>626.5157993094348</v>
       </c>
       <c r="D45">
-        <v>1192.500544753091</v>
+        <v>1184.471799309435</v>
       </c>
       <c r="E45">
-        <v>35.90700000000004</v>
+        <v>48.95600000000002</v>
       </c>
       <c r="F45">
-        <v>561.1070000000001</v>
+        <v>574.1560000000001</v>
       </c>
       <c r="G45">
         <v>16.2</v>
@@ -4971,37 +4971,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M45">
-        <v>82.37050760000002</v>
+        <v>84.28610080000001</v>
       </c>
       <c r="N45">
-        <v>-11.07050760000001</v>
+        <v>-12.9861008</v>
       </c>
       <c r="O45">
-        <v>-2.490864210000003</v>
+        <v>-2.921872680000001</v>
       </c>
       <c r="P45">
-        <v>-8.57964339000001</v>
+        <v>-10.06422812</v>
       </c>
       <c r="Q45">
-        <v>16.62035660999999</v>
+        <v>15.13577187999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.252586335661343</v>
+        <v>0.2562789487981527</v>
       </c>
       <c r="T45">
-        <v>1.441805846525845</v>
+        <v>1.467552379499521</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1947602420747981</v>
+        <v>0.1903338729367346</v>
       </c>
       <c r="W45">
-        <v>0.1182091964634196</v>
+        <v>0.1188589874528874</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8656010758879916</v>
+        <v>0.8459283241632647</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.195814165806236</v>
+        <v>0.196824165806236</v>
       </c>
       <c r="C46">
-        <v>626.5157993094348</v>
+        <v>605.5454410889405</v>
       </c>
       <c r="D46">
-        <v>1184.471799309435</v>
+        <v>1176.55044108894</v>
       </c>
       <c r="E46">
-        <v>48.95600000000002</v>
+        <v>62.005</v>
       </c>
       <c r="F46">
-        <v>574.1560000000001</v>
+        <v>587.205</v>
       </c>
       <c r="G46">
         <v>16.2</v>
@@ -5053,37 +5053,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M46">
-        <v>84.28610080000001</v>
+        <v>86.20169400000002</v>
       </c>
       <c r="N46">
-        <v>-12.9861008</v>
+        <v>-14.90169400000001</v>
       </c>
       <c r="O46">
-        <v>-2.921872680000001</v>
+        <v>-3.352881150000001</v>
       </c>
       <c r="P46">
-        <v>-10.06422812</v>
+        <v>-11.54881285</v>
       </c>
       <c r="Q46">
-        <v>15.13577187999999</v>
+        <v>13.65118714999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2562789487981527</v>
+        <v>0.2601058387763009</v>
       </c>
       <c r="T46">
-        <v>1.467552379499521</v>
+        <v>1.494235150035876</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1903338729367346</v>
+        <v>0.1861042313159182</v>
       </c>
       <c r="W46">
-        <v>0.1188589874528874</v>
+        <v>0.1194798988428232</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8459283241632647</v>
+        <v>0.8271299169596364</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.196824165806236</v>
+        <v>0.197834165806236</v>
       </c>
       <c r="C47">
-        <v>605.5454410889405</v>
+        <v>584.6803298931562</v>
       </c>
       <c r="D47">
-        <v>1176.55044108894</v>
+        <v>1168.734329893156</v>
       </c>
       <c r="E47">
-        <v>62.005</v>
+        <v>75.05399999999997</v>
       </c>
       <c r="F47">
-        <v>587.205</v>
+        <v>600.254</v>
       </c>
       <c r="G47">
         <v>16.2</v>
@@ -5135,37 +5135,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M47">
-        <v>86.20169400000002</v>
+        <v>88.11728720000001</v>
       </c>
       <c r="N47">
-        <v>-14.90169400000001</v>
+        <v>-16.8172872</v>
       </c>
       <c r="O47">
-        <v>-3.352881150000001</v>
+        <v>-3.783889619999999</v>
       </c>
       <c r="P47">
-        <v>-11.54881285</v>
+        <v>-13.03339758</v>
       </c>
       <c r="Q47">
-        <v>13.65118714999999</v>
+        <v>12.16660242</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2601058387763009</v>
+        <v>0.2640744654203065</v>
       </c>
       <c r="T47">
-        <v>1.494235150035876</v>
+        <v>1.521906171332837</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1861042313159182</v>
+        <v>0.1820584871568766</v>
       </c>
       <c r="W47">
-        <v>0.1194798988428232</v>
+        <v>0.1200738140853705</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8271299169596364</v>
+        <v>0.8091488318083402</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.197834165806236</v>
+        <v>0.2271213763069824</v>
       </c>
       <c r="C48">
-        <v>584.6803298931562</v>
+        <v>382.8561891117457</v>
       </c>
       <c r="D48">
-        <v>1168.734329893156</v>
+        <v>979.9591891117458</v>
       </c>
       <c r="E48">
-        <v>75.05399999999997</v>
+        <v>88.10300000000007</v>
       </c>
       <c r="F48">
-        <v>600.254</v>
+        <v>613.3030000000001</v>
       </c>
       <c r="G48">
         <v>16.2</v>
@@ -5217,45 +5217,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M48">
-        <v>88.11728720000001</v>
+        <v>123.1512424</v>
       </c>
       <c r="N48">
-        <v>-16.8172872</v>
+        <v>-51.85124240000002</v>
       </c>
       <c r="O48">
-        <v>-3.783889619999999</v>
+        <v>-11.66652954</v>
       </c>
       <c r="P48">
-        <v>-13.03339758</v>
+        <v>-40.18471286000001</v>
       </c>
       <c r="Q48">
-        <v>12.16660242</v>
+        <v>-14.98471286000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2640744654203065</v>
+        <v>0.273659286467381</v>
       </c>
       <c r="T48">
-        <v>1.521906171332837</v>
+        <v>1.588735785482044</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1820584871568766</v>
+        <v>0.1302666516988382</v>
       </c>
       <c r="W48">
-        <v>0.1200738140853705</v>
+        <v>0.1746424563388733</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8091488318083402</v>
+        <v>0.578962896439281</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2271213763069824</v>
+        <v>0.2286713763069824</v>
       </c>
       <c r="C49">
-        <v>382.8561891117457</v>
+        <v>361.5011503330286</v>
       </c>
       <c r="D49">
-        <v>979.9591891117458</v>
+        <v>971.6531503330286</v>
       </c>
       <c r="E49">
-        <v>88.10300000000007</v>
+        <v>101.152</v>
       </c>
       <c r="F49">
-        <v>613.3030000000001</v>
+        <v>626.3520000000001</v>
       </c>
       <c r="G49">
         <v>16.2</v>
@@ -5299,37 +5299,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M49">
-        <v>123.1512424</v>
+        <v>125.7714816</v>
       </c>
       <c r="N49">
-        <v>-51.85124240000002</v>
+        <v>-54.4714816</v>
       </c>
       <c r="O49">
-        <v>-11.66652954</v>
+        <v>-12.25608336</v>
       </c>
       <c r="P49">
-        <v>-40.18471286000001</v>
+        <v>-42.21539824</v>
       </c>
       <c r="Q49">
-        <v>-14.98471286000002</v>
+        <v>-17.01539824</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.273659286467381</v>
+        <v>0.278041195822523</v>
       </c>
       <c r="T49">
-        <v>1.588735785482044</v>
+        <v>1.619288396741314</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1302666516988382</v>
+        <v>0.1275527631217791</v>
       </c>
       <c r="W49">
-        <v>0.1746424563388733</v>
+        <v>0.1751874051651468</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.578962896439281</v>
+        <v>0.5669011694301294</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2286713763069824</v>
+        <v>0.2302213763069824</v>
       </c>
       <c r="C50">
-        <v>361.5011503330287</v>
+        <v>340.2857305113415</v>
       </c>
       <c r="D50">
-        <v>971.6531503330286</v>
+        <v>963.4867305113415</v>
       </c>
       <c r="E50">
-        <v>101.1519999999999</v>
+        <v>114.201</v>
       </c>
       <c r="F50">
-        <v>626.352</v>
+        <v>639.4010000000001</v>
       </c>
       <c r="G50">
         <v>16.2</v>
@@ -5381,37 +5381,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M50">
-        <v>125.7714816</v>
+        <v>128.3917208</v>
       </c>
       <c r="N50">
-        <v>-54.47148159999999</v>
+        <v>-57.09172080000002</v>
       </c>
       <c r="O50">
-        <v>-12.25608336</v>
+        <v>-12.84563718</v>
       </c>
       <c r="P50">
-        <v>-42.21539823999999</v>
+        <v>-44.24608362000001</v>
       </c>
       <c r="Q50">
-        <v>-17.01539824</v>
+        <v>-19.04608362000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.278041195822523</v>
+        <v>0.2825949447602195</v>
       </c>
       <c r="T50">
-        <v>1.619288396741314</v>
+        <v>1.651039149618594</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1275527631217791</v>
+        <v>0.1249496455070489</v>
       </c>
       <c r="W50">
-        <v>0.1751874051651468</v>
+        <v>0.1757101111821846</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5669011694301295</v>
+        <v>0.5553317578091064</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2302213763069824</v>
+        <v>0.2317713763069824</v>
       </c>
       <c r="C51">
-        <v>340.2857305113415</v>
+        <v>319.2064386355239</v>
       </c>
       <c r="D51">
-        <v>963.4867305113415</v>
+        <v>955.4564386355239</v>
       </c>
       <c r="E51">
-        <v>114.201</v>
+        <v>127.25</v>
       </c>
       <c r="F51">
-        <v>639.4010000000001</v>
+        <v>652.45</v>
       </c>
       <c r="G51">
         <v>16.2</v>
@@ -5463,37 +5463,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M51">
-        <v>128.3917208</v>
+        <v>131.01196</v>
       </c>
       <c r="N51">
-        <v>-57.09172080000002</v>
+        <v>-59.71196</v>
       </c>
       <c r="O51">
-        <v>-12.84563718</v>
+        <v>-13.435191</v>
       </c>
       <c r="P51">
-        <v>-44.24608362000001</v>
+        <v>-46.276769</v>
       </c>
       <c r="Q51">
-        <v>-19.04608362000002</v>
+        <v>-21.07676900000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2825949447602195</v>
+        <v>0.2873308436554239</v>
       </c>
       <c r="T51">
-        <v>1.651039149618594</v>
+        <v>1.684059932610966</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1249496455070489</v>
+        <v>0.1224506525969079</v>
       </c>
       <c r="W51">
-        <v>0.1757101111821846</v>
+        <v>0.1762119089585409</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5553317578091064</v>
+        <v>0.5442251226529242</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2317713763069824</v>
+        <v>0.2333213763069824</v>
       </c>
       <c r="C52">
-        <v>319.2064386355239</v>
+        <v>298.2598991173589</v>
       </c>
       <c r="D52">
-        <v>955.4564386355239</v>
+        <v>947.5588991173589</v>
       </c>
       <c r="E52">
-        <v>127.25</v>
+        <v>140.299</v>
       </c>
       <c r="F52">
-        <v>652.45</v>
+        <v>665.499</v>
       </c>
       <c r="G52">
         <v>16.2</v>
@@ -5545,37 +5545,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M52">
-        <v>131.01196</v>
+        <v>133.6321992</v>
       </c>
       <c r="N52">
-        <v>-59.71196</v>
+        <v>-62.33219919999999</v>
       </c>
       <c r="O52">
-        <v>-13.435191</v>
+        <v>-14.02474482</v>
       </c>
       <c r="P52">
-        <v>-46.276769</v>
+        <v>-48.30745438</v>
       </c>
       <c r="Q52">
-        <v>-21.07676900000001</v>
+        <v>-23.10745438</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2873308436554239</v>
+        <v>0.2922600445463509</v>
       </c>
       <c r="T52">
-        <v>1.684059932610966</v>
+        <v>1.718428502664251</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1224506525969079</v>
+        <v>0.1200496594087333</v>
       </c>
       <c r="W52">
-        <v>0.1762119089585409</v>
+        <v>0.1766940283907264</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5442251226529242</v>
+        <v>0.5335540418165925</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2333213763069824</v>
+        <v>0.2348713763069824</v>
       </c>
       <c r="C53">
-        <v>298.2598991173589</v>
+        <v>277.4428470604083</v>
       </c>
       <c r="D53">
-        <v>947.5588991173589</v>
+        <v>939.7908470604084</v>
       </c>
       <c r="E53">
-        <v>140.299</v>
+        <v>153.3480000000001</v>
       </c>
       <c r="F53">
-        <v>665.499</v>
+        <v>678.5480000000001</v>
       </c>
       <c r="G53">
         <v>16.2</v>
@@ -5627,37 +5627,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M53">
-        <v>133.6321992</v>
+        <v>136.2524384</v>
       </c>
       <c r="N53">
-        <v>-62.33219919999999</v>
+        <v>-64.95243840000001</v>
       </c>
       <c r="O53">
-        <v>-14.02474482</v>
+        <v>-14.61429864</v>
       </c>
       <c r="P53">
-        <v>-48.30745438</v>
+        <v>-50.33813976</v>
       </c>
       <c r="Q53">
-        <v>-23.10745438</v>
+        <v>-25.13813976000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2922600445463509</v>
+        <v>0.2973946288077333</v>
       </c>
       <c r="T53">
-        <v>1.718428502664251</v>
+        <v>1.754229096469757</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1200496594087333</v>
+        <v>0.1177410121124115</v>
       </c>
       <c r="W53">
-        <v>0.1766940283907264</v>
+        <v>0.1771576047678278</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5335540418165925</v>
+        <v>0.5232933871662733</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2348713763069824</v>
+        <v>0.2364213763069824</v>
       </c>
       <c r="C54">
-        <v>277.4428470604083</v>
+        <v>256.7521237596713</v>
       </c>
       <c r="D54">
-        <v>939.7908470604084</v>
+        <v>932.1491237596714</v>
       </c>
       <c r="E54">
-        <v>153.3480000000001</v>
+        <v>166.397</v>
       </c>
       <c r="F54">
-        <v>678.5480000000001</v>
+        <v>691.5970000000001</v>
       </c>
       <c r="G54">
         <v>16.2</v>
@@ -5709,37 +5709,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M54">
-        <v>136.2524384</v>
+        <v>138.8726776</v>
       </c>
       <c r="N54">
-        <v>-64.95243840000001</v>
+        <v>-67.57267760000002</v>
       </c>
       <c r="O54">
-        <v>-14.61429864</v>
+        <v>-15.20385246000001</v>
       </c>
       <c r="P54">
-        <v>-50.33813976</v>
+        <v>-52.36882514000001</v>
       </c>
       <c r="Q54">
-        <v>-25.13813976000001</v>
+        <v>-27.16882514000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2973946288077333</v>
+        <v>0.3027477060164084</v>
       </c>
       <c r="T54">
-        <v>1.754229096469757</v>
+        <v>1.791553119798901</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1177410121124115</v>
+        <v>0.1155194835819886</v>
       </c>
       <c r="W54">
-        <v>0.1771576047678278</v>
+        <v>0.1776036876967367</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5232933871662733</v>
+        <v>0.5134199270310605</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2364213763069824</v>
+        <v>0.2379713763069824</v>
       </c>
       <c r="C55">
-        <v>256.7521237596713</v>
+        <v>236.1846724190333</v>
       </c>
       <c r="D55">
-        <v>932.1491237596714</v>
+        <v>924.6306724190333</v>
       </c>
       <c r="E55">
-        <v>166.397</v>
+        <v>179.446</v>
       </c>
       <c r="F55">
-        <v>691.5970000000001</v>
+        <v>704.6460000000001</v>
       </c>
       <c r="G55">
         <v>16.2</v>
@@ -5791,37 +5791,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M55">
-        <v>138.8726776</v>
+        <v>141.4929168</v>
       </c>
       <c r="N55">
-        <v>-67.57267760000002</v>
+        <v>-70.19291680000001</v>
       </c>
       <c r="O55">
-        <v>-15.20385246000001</v>
+        <v>-15.79340628</v>
       </c>
       <c r="P55">
-        <v>-52.36882514000001</v>
+        <v>-54.39951052000001</v>
       </c>
       <c r="Q55">
-        <v>-27.16882514000002</v>
+        <v>-29.19951052000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3027477060164084</v>
+        <v>0.3083335257124173</v>
       </c>
       <c r="T55">
-        <v>1.791553119798901</v>
+        <v>1.83049992675105</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1155194835819886</v>
+        <v>0.1133802338860259</v>
       </c>
       <c r="W55">
-        <v>0.1776036876967367</v>
+        <v>0.178033249035686</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5134199270310605</v>
+        <v>0.5039121506045594</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2379713763069824</v>
+        <v>0.2599404357384557</v>
       </c>
       <c r="C56">
-        <v>236.1846724190333</v>
+        <v>128.2761185730384</v>
       </c>
       <c r="D56">
-        <v>924.6306724190333</v>
+        <v>829.7711185730385</v>
       </c>
       <c r="E56">
-        <v>179.446</v>
+        <v>192.4950000000001</v>
       </c>
       <c r="F56">
-        <v>704.6460000000001</v>
+        <v>717.6950000000002</v>
       </c>
       <c r="G56">
         <v>16.2</v>
@@ -5873,45 +5873,45 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M56">
-        <v>141.4929168</v>
+        <v>169.232481</v>
       </c>
       <c r="N56">
-        <v>-70.19291680000001</v>
+        <v>-97.93248100000002</v>
       </c>
       <c r="O56">
-        <v>-15.79340628</v>
+        <v>-22.03480822500001</v>
       </c>
       <c r="P56">
-        <v>-54.39951052000001</v>
+        <v>-75.89767277500002</v>
       </c>
       <c r="Q56">
-        <v>-29.19951052000001</v>
+        <v>-50.69767277500002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3083335257124173</v>
+        <v>0.3167655139093005</v>
       </c>
       <c r="T56">
-        <v>1.83049992675105</v>
+        <v>1.889291480076959</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1133802338860259</v>
+        <v>0.0947956320512727</v>
       </c>
       <c r="W56">
-        <v>0.178033249035686</v>
+        <v>0.2134471899623099</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.5039121506045594</v>
+        <v>0.4213139202278787</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2599404357384557</v>
+        <v>0.2618404357384557</v>
       </c>
       <c r="C57">
-        <v>128.2761185730384</v>
+        <v>107.9295720748568</v>
       </c>
       <c r="D57">
-        <v>829.7711185730385</v>
+        <v>822.4735720748569</v>
       </c>
       <c r="E57">
-        <v>192.4950000000001</v>
+        <v>205.5440000000001</v>
       </c>
       <c r="F57">
-        <v>717.6950000000002</v>
+        <v>730.7440000000001</v>
       </c>
       <c r="G57">
         <v>16.2</v>
@@ -5955,37 +5955,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M57">
-        <v>169.232481</v>
+        <v>172.3094352000001</v>
       </c>
       <c r="N57">
-        <v>-97.93248100000002</v>
+        <v>-101.0094352</v>
       </c>
       <c r="O57">
-        <v>-22.03480822500001</v>
+        <v>-22.72712292000001</v>
       </c>
       <c r="P57">
-        <v>-75.89767277500002</v>
+        <v>-78.28231228000003</v>
       </c>
       <c r="Q57">
-        <v>-50.69767277500002</v>
+        <v>-53.08231228000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3167655139093005</v>
+        <v>0.3229238210436027</v>
       </c>
       <c r="T57">
-        <v>1.889291480076959</v>
+        <v>1.932229922805981</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.0947956320512727</v>
+        <v>0.09310285290749998</v>
       </c>
       <c r="W57">
-        <v>0.2134471899623099</v>
+        <v>0.2138463472844115</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4213139202278787</v>
+        <v>0.4137904573666665</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2618404357384557</v>
+        <v>0.2637404357384556</v>
       </c>
       <c r="C58">
-        <v>107.9295720748568</v>
+        <v>87.7102652814101</v>
       </c>
       <c r="D58">
-        <v>822.4735720748569</v>
+        <v>815.3032652814102</v>
       </c>
       <c r="E58">
-        <v>205.5440000000001</v>
+        <v>218.5930000000001</v>
       </c>
       <c r="F58">
-        <v>730.7440000000001</v>
+        <v>743.7930000000001</v>
       </c>
       <c r="G58">
         <v>16.2</v>
@@ -6037,37 +6037,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M58">
-        <v>172.3094352000001</v>
+        <v>175.3863894</v>
       </c>
       <c r="N58">
-        <v>-101.0094352</v>
+        <v>-104.0863894</v>
       </c>
       <c r="O58">
-        <v>-22.72712292000001</v>
+        <v>-23.41943761500001</v>
       </c>
       <c r="P58">
-        <v>-78.28231228000003</v>
+        <v>-80.66695178500002</v>
       </c>
       <c r="Q58">
-        <v>-53.08231228000003</v>
+        <v>-55.46695178500003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3229238210436027</v>
+        <v>0.3293685610678725</v>
       </c>
       <c r="T58">
-        <v>1.932229922805981</v>
+        <v>1.97716550240612</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09310285290749998</v>
+        <v>0.09146946952315788</v>
       </c>
       <c r="W58">
-        <v>0.2138463472844115</v>
+        <v>0.2142314990864394</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4137904573666665</v>
+        <v>0.4065309756584794</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2637404357384556</v>
+        <v>0.2656404357384557</v>
       </c>
       <c r="C59">
-        <v>87.7102652814101</v>
+        <v>67.61489913483967</v>
       </c>
       <c r="D59">
-        <v>815.3032652814102</v>
+        <v>808.2568991348397</v>
       </c>
       <c r="E59">
-        <v>218.5930000000001</v>
+        <v>231.6420000000001</v>
       </c>
       <c r="F59">
-        <v>743.7930000000001</v>
+        <v>756.8420000000001</v>
       </c>
       <c r="G59">
         <v>16.2</v>
@@ -6119,37 +6119,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M59">
-        <v>175.3863894</v>
+        <v>178.4633436</v>
       </c>
       <c r="N59">
-        <v>-104.0863894</v>
+        <v>-107.1633436</v>
       </c>
       <c r="O59">
-        <v>-23.41943761500001</v>
+        <v>-24.11175231</v>
       </c>
       <c r="P59">
-        <v>-80.66695178500002</v>
+        <v>-83.05159129000002</v>
       </c>
       <c r="Q59">
-        <v>-55.46695178500003</v>
+        <v>-57.85159129000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3293685610678725</v>
+        <v>0.3361201934742505</v>
       </c>
       <c r="T59">
-        <v>1.97716550240612</v>
+        <v>2.024240871511028</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09146946952315788</v>
+        <v>0.08989240970379309</v>
       </c>
       <c r="W59">
-        <v>0.2142314990864394</v>
+        <v>0.2146033697918456</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4065309756584794</v>
+        <v>0.3995218209057471</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2656404357384556</v>
+        <v>0.2675404357384557</v>
       </c>
       <c r="C60">
-        <v>67.61489913484036</v>
+        <v>47.64028765021419</v>
       </c>
       <c r="D60">
-        <v>808.2568991348403</v>
+        <v>801.3312876502141</v>
       </c>
       <c r="E60">
-        <v>231.6419999999999</v>
+        <v>244.6909999999999</v>
       </c>
       <c r="F60">
-        <v>756.842</v>
+        <v>769.891</v>
       </c>
       <c r="G60">
         <v>16.2</v>
@@ -6201,37 +6201,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M60">
-        <v>178.4633436</v>
+        <v>181.5402978</v>
       </c>
       <c r="N60">
-        <v>-107.1633436</v>
+        <v>-110.2402978</v>
       </c>
       <c r="O60">
-        <v>-24.11175231</v>
+        <v>-24.804067005</v>
       </c>
       <c r="P60">
-        <v>-83.05159128999999</v>
+        <v>-85.43623079499999</v>
       </c>
       <c r="Q60">
-        <v>-57.85159128999999</v>
+        <v>-60.23623079499999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3361201934742504</v>
+        <v>0.3432011738028906</v>
       </c>
       <c r="T60">
-        <v>2.024240871511027</v>
+        <v>2.073612600084466</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0898924097037931</v>
+        <v>0.08836880953932204</v>
       </c>
       <c r="W60">
-        <v>0.2146033697918456</v>
+        <v>0.2149626347106279</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3995218209057471</v>
+        <v>0.392750264619209</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2675404357384557</v>
+        <v>0.2694404357384557</v>
       </c>
       <c r="C61">
-        <v>47.64028765021419</v>
+        <v>27.78335311231149</v>
       </c>
       <c r="D61">
-        <v>801.3312876502141</v>
+        <v>794.5233531123115</v>
       </c>
       <c r="E61">
-        <v>244.6909999999999</v>
+        <v>257.74</v>
       </c>
       <c r="F61">
-        <v>769.891</v>
+        <v>782.9400000000001</v>
       </c>
       <c r="G61">
         <v>16.2</v>
@@ -6283,37 +6283,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M61">
-        <v>181.5402978</v>
+        <v>184.617252</v>
       </c>
       <c r="N61">
-        <v>-110.2402978</v>
+        <v>-113.317252</v>
       </c>
       <c r="O61">
-        <v>-24.804067005</v>
+        <v>-25.4963817</v>
       </c>
       <c r="P61">
-        <v>-85.43623079499999</v>
+        <v>-87.8208703</v>
       </c>
       <c r="Q61">
-        <v>-60.23623079499999</v>
+        <v>-62.6208703</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3432011738028906</v>
+        <v>0.350636203147963</v>
       </c>
       <c r="T61">
-        <v>2.073612600084466</v>
+        <v>2.125452915086579</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08836880953932204</v>
+        <v>0.08689599604699999</v>
       </c>
       <c r="W61">
-        <v>0.2149626347106279</v>
+        <v>0.2153099241321174</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.392750264619209</v>
+        <v>0.3862044268755556</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2694404357384557</v>
+        <v>0.2713404357384557</v>
       </c>
       <c r="C62">
-        <v>27.78335311231149</v>
+        <v>8.041121515189047</v>
       </c>
       <c r="D62">
-        <v>794.5233531123115</v>
+        <v>787.830121515189</v>
       </c>
       <c r="E62">
-        <v>257.74</v>
+        <v>270.789</v>
       </c>
       <c r="F62">
-        <v>782.9400000000001</v>
+        <v>795.989</v>
       </c>
       <c r="G62">
         <v>16.2</v>
@@ -6365,37 +6365,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M62">
-        <v>184.617252</v>
+        <v>187.6942062</v>
       </c>
       <c r="N62">
-        <v>-113.317252</v>
+        <v>-116.3942062</v>
       </c>
       <c r="O62">
-        <v>-25.4963817</v>
+        <v>-26.188696395</v>
       </c>
       <c r="P62">
-        <v>-87.8208703</v>
+        <v>-90.20550980500001</v>
       </c>
       <c r="Q62">
-        <v>-62.6208703</v>
+        <v>-65.005509805</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.350636203147963</v>
+        <v>0.3584525160491928</v>
       </c>
       <c r="T62">
-        <v>2.125452915086579</v>
+        <v>2.179951707781106</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08689599604699999</v>
+        <v>0.08547147152163934</v>
       </c>
       <c r="W62">
-        <v>0.2153099241321174</v>
+        <v>0.2156458270151974</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3862044268755556</v>
+        <v>0.3798732067628414</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2713404357384557</v>
+        <v>0.2732404357384556</v>
       </c>
       <c r="C63">
-        <v>8.041121515189047</v>
+        <v>-11.58928176966992</v>
       </c>
       <c r="D63">
-        <v>787.830121515189</v>
+        <v>781.24871823033</v>
       </c>
       <c r="E63">
-        <v>270.789</v>
+        <v>283.838</v>
       </c>
       <c r="F63">
-        <v>795.989</v>
+        <v>809.038</v>
       </c>
       <c r="G63">
         <v>16.2</v>
@@ -6447,37 +6447,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M63">
-        <v>187.6942062</v>
+        <v>190.7711604</v>
       </c>
       <c r="N63">
-        <v>-116.3942062</v>
+        <v>-119.4711604</v>
       </c>
       <c r="O63">
-        <v>-26.188696395</v>
+        <v>-26.88101109</v>
       </c>
       <c r="P63">
-        <v>-90.20550980500001</v>
+        <v>-92.59014931</v>
       </c>
       <c r="Q63">
-        <v>-65.005509805</v>
+        <v>-67.39014931</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3584525160491928</v>
+        <v>0.366680213839961</v>
       </c>
       <c r="T63">
-        <v>2.179951707781106</v>
+        <v>2.237318857985872</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08547147152163934</v>
+        <v>0.08409289940032258</v>
       </c>
       <c r="W63">
-        <v>0.2156458270151974</v>
+        <v>0.2159708943214039</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3798732067628414</v>
+        <v>0.3737462195569892</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2732404357384556</v>
+        <v>0.2751404357384556</v>
       </c>
       <c r="C64">
-        <v>-11.58928176966992</v>
+        <v>-31.11063610988083</v>
       </c>
       <c r="D64">
-        <v>781.24871823033</v>
+        <v>774.7763638901192</v>
       </c>
       <c r="E64">
-        <v>283.838</v>
+        <v>296.8870000000001</v>
       </c>
       <c r="F64">
-        <v>809.038</v>
+        <v>822.0870000000001</v>
       </c>
       <c r="G64">
         <v>16.2</v>
@@ -6529,37 +6529,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M64">
-        <v>190.7711604</v>
+        <v>193.8481146</v>
       </c>
       <c r="N64">
-        <v>-119.4711604</v>
+        <v>-122.5481146</v>
       </c>
       <c r="O64">
-        <v>-26.88101109</v>
+        <v>-27.57332578500001</v>
       </c>
       <c r="P64">
-        <v>-92.59014931</v>
+        <v>-94.97478881500001</v>
       </c>
       <c r="Q64">
-        <v>-67.39014931</v>
+        <v>-69.77478881500002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.366680213839961</v>
+        <v>0.3753526520518519</v>
       </c>
       <c r="T64">
-        <v>2.237318857985872</v>
+        <v>2.297786935228733</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08409289940032258</v>
+        <v>0.08275809147333332</v>
       </c>
       <c r="W64">
-        <v>0.2159708943214039</v>
+        <v>0.216285642030588</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3737462195569892</v>
+        <v>0.3678137398814815</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2751404357384556</v>
+        <v>0.2770404357384557</v>
       </c>
       <c r="C65">
-        <v>-31.11063610988083</v>
+        <v>-50.52562952573919</v>
       </c>
       <c r="D65">
-        <v>774.7763638901192</v>
+        <v>768.4103704742608</v>
       </c>
       <c r="E65">
-        <v>296.8870000000001</v>
+        <v>309.936</v>
       </c>
       <c r="F65">
-        <v>822.0870000000001</v>
+        <v>835.1360000000001</v>
       </c>
       <c r="G65">
         <v>16.2</v>
@@ -6611,37 +6611,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M65">
-        <v>193.8481146</v>
+        <v>196.9250688</v>
       </c>
       <c r="N65">
-        <v>-122.5481146</v>
+        <v>-125.6250688</v>
       </c>
       <c r="O65">
-        <v>-27.57332578500001</v>
+        <v>-28.26564048</v>
       </c>
       <c r="P65">
-        <v>-94.97478881500001</v>
+        <v>-97.35942832000001</v>
       </c>
       <c r="Q65">
-        <v>-69.77478881500002</v>
+        <v>-72.15942832000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3753526520518519</v>
+        <v>0.3845068923866256</v>
       </c>
       <c r="T65">
-        <v>2.297786935228733</v>
+        <v>2.361614350096199</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08275809147333332</v>
+        <v>0.08146499629406249</v>
       </c>
       <c r="W65">
-        <v>0.216285642030588</v>
+        <v>0.2165905538738601</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3678137398814815</v>
+        <v>0.3620666501958333</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2770404357384557</v>
+        <v>0.2789404357384556</v>
       </c>
       <c r="C66">
-        <v>-50.52562952573919</v>
+        <v>-69.83686241243981</v>
       </c>
       <c r="D66">
-        <v>768.4103704742608</v>
+        <v>762.1481375875602</v>
       </c>
       <c r="E66">
-        <v>309.936</v>
+        <v>322.985</v>
       </c>
       <c r="F66">
-        <v>835.1360000000001</v>
+        <v>848.1850000000001</v>
       </c>
       <c r="G66">
         <v>16.2</v>
@@ -6693,37 +6693,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M66">
-        <v>196.9250688</v>
+        <v>200.002023</v>
       </c>
       <c r="N66">
-        <v>-125.6250688</v>
+        <v>-128.702023</v>
       </c>
       <c r="O66">
-        <v>-28.26564048</v>
+        <v>-28.957955175</v>
       </c>
       <c r="P66">
-        <v>-97.35942832000001</v>
+        <v>-99.744067825</v>
       </c>
       <c r="Q66">
-        <v>-72.15942832000002</v>
+        <v>-74.54406782500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3845068923866256</v>
+        <v>0.3941842321691006</v>
       </c>
       <c r="T66">
-        <v>2.361614350096199</v>
+        <v>2.429089045813233</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08146499629406249</v>
+        <v>0.08021168865876922</v>
       </c>
       <c r="W66">
-        <v>0.2165905538738601</v>
+        <v>0.2168860838142622</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3620666501958333</v>
+        <v>0.3564963940389744</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2789404357384556</v>
+        <v>0.2808404357384556</v>
       </c>
       <c r="C67">
-        <v>-69.83686241243981</v>
+        <v>-89.04685108175863</v>
       </c>
       <c r="D67">
-        <v>762.1481375875602</v>
+        <v>755.9871489182415</v>
       </c>
       <c r="E67">
-        <v>322.985</v>
+        <v>336.0340000000001</v>
       </c>
       <c r="F67">
-        <v>848.1850000000001</v>
+        <v>861.2340000000002</v>
       </c>
       <c r="G67">
         <v>16.2</v>
@@ -6775,37 +6775,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M67">
-        <v>200.002023</v>
+        <v>203.0789772000001</v>
       </c>
       <c r="N67">
-        <v>-128.702023</v>
+        <v>-131.7789772</v>
       </c>
       <c r="O67">
-        <v>-28.957955175</v>
+        <v>-29.65026987000001</v>
       </c>
       <c r="P67">
-        <v>-99.744067825</v>
+        <v>-102.12870733</v>
       </c>
       <c r="Q67">
-        <v>-74.54406782500001</v>
+        <v>-76.92870733000004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3941842321691006</v>
+        <v>0.4044308272328977</v>
       </c>
       <c r="T67">
-        <v>2.429089045813233</v>
+        <v>2.500532841278328</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08021168865876922</v>
+        <v>0.07899636004272725</v>
       </c>
       <c r="W67">
-        <v>0.2168860838142622</v>
+        <v>0.2171726583019249</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3564963940389744</v>
+        <v>0.3510949335232322</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2808404357384556</v>
+        <v>0.2827404357384556</v>
       </c>
       <c r="C68">
-        <v>-89.04685108175863</v>
+        <v>-108.1580311333316</v>
       </c>
       <c r="D68">
-        <v>755.9871489182415</v>
+        <v>749.9249688666685</v>
       </c>
       <c r="E68">
-        <v>336.0340000000001</v>
+        <v>349.0830000000001</v>
       </c>
       <c r="F68">
-        <v>861.2340000000002</v>
+        <v>874.2830000000001</v>
       </c>
       <c r="G68">
         <v>16.2</v>
@@ -6857,37 +6857,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M68">
-        <v>203.0789772000001</v>
+        <v>206.1559314</v>
       </c>
       <c r="N68">
-        <v>-131.7789772</v>
+        <v>-134.8559314</v>
       </c>
       <c r="O68">
-        <v>-29.65026987000001</v>
+        <v>-30.34258456500001</v>
       </c>
       <c r="P68">
-        <v>-102.12870733</v>
+        <v>-104.513346835</v>
       </c>
       <c r="Q68">
-        <v>-76.92870733000004</v>
+        <v>-79.31334683500003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4044308272328977</v>
+        <v>0.415298428058137</v>
       </c>
       <c r="T68">
-        <v>2.500532841278328</v>
+        <v>2.576306563741308</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07899636004272725</v>
+        <v>0.07781730989283581</v>
       </c>
       <c r="W68">
-        <v>0.2171726583019249</v>
+        <v>0.2174506783272693</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3510949335232322</v>
+        <v>0.3458547106348258</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2827404357384556</v>
+        <v>0.2846404357384557</v>
       </c>
       <c r="C69">
-        <v>-108.1580311333316</v>
+        <v>-127.1727606650218</v>
       </c>
       <c r="D69">
-        <v>749.9249688666685</v>
+        <v>743.9592393349783</v>
       </c>
       <c r="E69">
-        <v>349.0830000000001</v>
+        <v>362.1320000000001</v>
       </c>
       <c r="F69">
-        <v>874.2830000000001</v>
+        <v>887.3320000000001</v>
       </c>
       <c r="G69">
         <v>16.2</v>
@@ -6939,37 +6939,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M69">
-        <v>206.1559314</v>
+        <v>209.2328856</v>
       </c>
       <c r="N69">
-        <v>-134.8559314</v>
+        <v>-137.9328856</v>
       </c>
       <c r="O69">
-        <v>-30.34258456500001</v>
+        <v>-31.03489926000001</v>
       </c>
       <c r="P69">
-        <v>-104.513346835</v>
+        <v>-106.89798634</v>
       </c>
       <c r="Q69">
-        <v>-79.31334683500003</v>
+        <v>-81.69798634000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.415298428058137</v>
+        <v>0.4268452539349538</v>
       </c>
       <c r="T69">
-        <v>2.576306563741308</v>
+        <v>2.656816143858224</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07781730989283581</v>
+        <v>0.0766729376885294</v>
       </c>
       <c r="W69">
-        <v>0.2174506783272693</v>
+        <v>0.2177205212930448</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3458547106348258</v>
+        <v>0.3407686119490195</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2846404357384557</v>
+        <v>0.2865404357384557</v>
       </c>
       <c r="C70">
-        <v>-127.1727606650218</v>
+        <v>-146.0933233312627</v>
       </c>
       <c r="D70">
-        <v>743.9592393349783</v>
+        <v>738.0876766687373</v>
       </c>
       <c r="E70">
-        <v>362.1320000000001</v>
+        <v>375.181</v>
       </c>
       <c r="F70">
-        <v>887.3320000000001</v>
+        <v>900.3810000000001</v>
       </c>
       <c r="G70">
         <v>16.2</v>
@@ -7021,37 +7021,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M70">
-        <v>209.2328856</v>
+        <v>212.3098398</v>
       </c>
       <c r="N70">
-        <v>-137.9328856</v>
+        <v>-141.0098398</v>
       </c>
       <c r="O70">
-        <v>-31.03489926000001</v>
+        <v>-31.727213955</v>
       </c>
       <c r="P70">
-        <v>-106.89798634</v>
+        <v>-109.282625845</v>
       </c>
       <c r="Q70">
-        <v>-81.69798634000003</v>
+        <v>-84.08262584500002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4268452539349538</v>
+        <v>0.4391370363199524</v>
       </c>
       <c r="T70">
-        <v>2.656816143858224</v>
+        <v>2.742519890434296</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0766729376885294</v>
+        <v>0.07556173569304347</v>
       </c>
       <c r="W70">
-        <v>0.2177205212930448</v>
+        <v>0.2179825427235804</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3407686119490195</v>
+        <v>0.3358299364135265</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2865404357384557</v>
+        <v>0.2884404357384557</v>
       </c>
       <c r="C71">
-        <v>-146.0933233312627</v>
+        <v>-164.9219312577101</v>
       </c>
       <c r="D71">
-        <v>738.0876766687373</v>
+        <v>732.3080687422901</v>
       </c>
       <c r="E71">
-        <v>375.181</v>
+        <v>388.2300000000001</v>
       </c>
       <c r="F71">
-        <v>900.3810000000001</v>
+        <v>913.4300000000002</v>
       </c>
       <c r="G71">
         <v>16.2</v>
@@ -7103,37 +7103,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M71">
-        <v>212.3098398</v>
+        <v>215.386794</v>
       </c>
       <c r="N71">
-        <v>-141.0098398</v>
+        <v>-144.086794</v>
       </c>
       <c r="O71">
-        <v>-31.727213955</v>
+        <v>-32.41952865</v>
       </c>
       <c r="P71">
-        <v>-109.282625845</v>
+        <v>-111.66726535</v>
       </c>
       <c r="Q71">
-        <v>-84.08262584500002</v>
+        <v>-86.46726535000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4391370363199524</v>
+        <v>0.4522482708639508</v>
       </c>
       <c r="T71">
-        <v>2.742519890434296</v>
+        <v>2.833937220115439</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07556173569304347</v>
+        <v>0.07448228232599999</v>
       </c>
       <c r="W71">
-        <v>0.2179825427235804</v>
+        <v>0.2182370778275292</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3358299364135265</v>
+        <v>0.3310323658933333</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2884404357384557</v>
+        <v>0.2903404357384556</v>
       </c>
       <c r="C72">
-        <v>-164.9219312577101</v>
+        <v>-183.6607278200195</v>
       </c>
       <c r="D72">
-        <v>732.3080687422901</v>
+        <v>726.6182721799806</v>
       </c>
       <c r="E72">
-        <v>388.2300000000001</v>
+        <v>401.2790000000001</v>
       </c>
       <c r="F72">
-        <v>913.4300000000002</v>
+        <v>926.4790000000002</v>
       </c>
       <c r="G72">
         <v>16.2</v>
@@ -7185,37 +7185,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M72">
-        <v>215.386794</v>
+        <v>218.4637482000001</v>
       </c>
       <c r="N72">
-        <v>-144.086794</v>
+        <v>-147.1637482</v>
       </c>
       <c r="O72">
-        <v>-32.41952865</v>
+        <v>-33.11184334500001</v>
       </c>
       <c r="P72">
-        <v>-111.66726535</v>
+        <v>-114.051904855</v>
       </c>
       <c r="Q72">
-        <v>-86.46726535000002</v>
+        <v>-88.85190485500004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4522482708639508</v>
+        <v>0.466263728479949</v>
       </c>
       <c r="T72">
-        <v>2.833937220115439</v>
+        <v>2.931659193222868</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07448228232599999</v>
+        <v>0.07343323609605631</v>
       </c>
       <c r="W72">
-        <v>0.2182370778275292</v>
+        <v>0.2184844429285499</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3310323658933333</v>
+        <v>0.3263699382046947</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2903404357384556</v>
+        <v>0.2922404357384557</v>
       </c>
       <c r="C73">
-        <v>-183.6607278200194</v>
+        <v>-202.3117902940817</v>
       </c>
       <c r="D73">
-        <v>726.6182721799806</v>
+        <v>721.0162097059183</v>
       </c>
       <c r="E73">
-        <v>401.279</v>
+        <v>414.328</v>
       </c>
       <c r="F73">
-        <v>926.479</v>
+        <v>939.528</v>
       </c>
       <c r="G73">
         <v>16.2</v>
@@ -7267,37 +7267,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M73">
-        <v>218.4637482</v>
+        <v>221.5407024</v>
       </c>
       <c r="N73">
-        <v>-147.1637482</v>
+        <v>-150.2407024</v>
       </c>
       <c r="O73">
-        <v>-33.111843345</v>
+        <v>-33.80415804</v>
       </c>
       <c r="P73">
-        <v>-114.051904855</v>
+        <v>-116.43654436</v>
       </c>
       <c r="Q73">
-        <v>-88.85190485500002</v>
+        <v>-91.23654436000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4662637284799489</v>
+        <v>0.4812802902113756</v>
       </c>
       <c r="T73">
-        <v>2.931659193222867</v>
+        <v>3.036361307266541</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07343323609605633</v>
+        <v>0.07241333003916665</v>
       </c>
       <c r="W73">
-        <v>0.2184844429285499</v>
+        <v>0.2187249367767645</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3263699382046948</v>
+        <v>0.3218370223962963</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2922404357384557</v>
+        <v>0.2941404357384556</v>
       </c>
       <c r="C74">
-        <v>-202.3117902940817</v>
+        <v>-220.8771323845981</v>
       </c>
       <c r="D74">
-        <v>721.0162097059183</v>
+        <v>715.4998676154019</v>
       </c>
       <c r="E74">
-        <v>414.328</v>
+        <v>427.377</v>
       </c>
       <c r="F74">
-        <v>939.528</v>
+        <v>952.577</v>
       </c>
       <c r="G74">
         <v>16.2</v>
@@ -7349,37 +7349,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M74">
-        <v>221.5407024</v>
+        <v>224.6176566</v>
       </c>
       <c r="N74">
-        <v>-150.2407024</v>
+        <v>-153.3176566</v>
       </c>
       <c r="O74">
-        <v>-33.80415804</v>
+        <v>-34.496472735</v>
       </c>
       <c r="P74">
-        <v>-116.43654436</v>
+        <v>-118.821183865</v>
       </c>
       <c r="Q74">
-        <v>-91.23654436000001</v>
+        <v>-93.62118386500001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4812802902113756</v>
+        <v>0.497409189848834</v>
       </c>
       <c r="T74">
-        <v>3.036361307266541</v>
+        <v>3.148819133461597</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07241333003916665</v>
+        <v>0.0714213666139726</v>
       </c>
       <c r="W74">
-        <v>0.2187249367767645</v>
+        <v>0.2189588417524253</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3218370223962963</v>
+        <v>0.3174282960621004</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2941404357384556</v>
+        <v>0.2960404357384556</v>
       </c>
       <c r="C75">
-        <v>-220.8771323845981</v>
+        <v>-239.3587066384654</v>
       </c>
       <c r="D75">
-        <v>715.4998676154019</v>
+        <v>710.0672933615347</v>
       </c>
       <c r="E75">
-        <v>427.377</v>
+        <v>440.426</v>
       </c>
       <c r="F75">
-        <v>952.577</v>
+        <v>965.6260000000001</v>
       </c>
       <c r="G75">
         <v>16.2</v>
@@ -7431,37 +7431,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M75">
-        <v>224.6176566</v>
+        <v>227.6946108</v>
       </c>
       <c r="N75">
-        <v>-153.3176566</v>
+        <v>-156.3946108</v>
       </c>
       <c r="O75">
-        <v>-34.496472735</v>
+        <v>-35.18878743</v>
       </c>
       <c r="P75">
-        <v>-118.821183865</v>
+        <v>-121.20582337</v>
       </c>
       <c r="Q75">
-        <v>-93.62118386500001</v>
+        <v>-96.00582337</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.497409189848834</v>
+        <v>0.5147787740737891</v>
       </c>
       <c r="T75">
-        <v>3.148819133461597</v>
+        <v>3.269927561671659</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0714213666139726</v>
+        <v>0.07045621301108108</v>
       </c>
       <c r="W75">
-        <v>0.2189588417524253</v>
+        <v>0.2191864249719871</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3174282960621004</v>
+        <v>0.3131387244936936</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2960404357384556</v>
+        <v>0.2979404357384556</v>
       </c>
       <c r="C76">
-        <v>-239.3587066384654</v>
+        <v>-257.7584067490434</v>
       </c>
       <c r="D76">
-        <v>710.0672933615347</v>
+        <v>704.7165932509566</v>
       </c>
       <c r="E76">
-        <v>440.426</v>
+        <v>453.475</v>
       </c>
       <c r="F76">
-        <v>965.6260000000001</v>
+        <v>978.6750000000001</v>
       </c>
       <c r="G76">
         <v>16.2</v>
@@ -7513,37 +7513,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M76">
-        <v>227.6946108</v>
+        <v>230.771565</v>
       </c>
       <c r="N76">
-        <v>-156.3946108</v>
+        <v>-159.471565</v>
       </c>
       <c r="O76">
-        <v>-35.18878743</v>
+        <v>-35.88110212500001</v>
       </c>
       <c r="P76">
-        <v>-121.20582337</v>
+        <v>-123.590462875</v>
       </c>
       <c r="Q76">
-        <v>-96.00582337</v>
+        <v>-98.39046287500003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5147787740737891</v>
+        <v>0.5335379250367408</v>
       </c>
       <c r="T76">
-        <v>3.269927561671659</v>
+        <v>3.400724664138526</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07045621301108108</v>
+        <v>0.06951679683759998</v>
       </c>
       <c r="W76">
-        <v>0.2191864249719871</v>
+        <v>0.2194079393056939</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3131387244936936</v>
+        <v>0.3089635415004444</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2979404357384556</v>
+        <v>0.2998404357384556</v>
       </c>
       <c r="C77">
-        <v>-257.7584067490434</v>
+        <v>-276.0780697570194</v>
       </c>
       <c r="D77">
-        <v>704.7165932509566</v>
+        <v>699.4459302429806</v>
       </c>
       <c r="E77">
-        <v>453.475</v>
+        <v>466.524</v>
       </c>
       <c r="F77">
-        <v>978.6750000000001</v>
+        <v>991.724</v>
       </c>
       <c r="G77">
         <v>16.2</v>
@@ -7595,37 +7595,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M77">
-        <v>230.771565</v>
+        <v>233.8485192</v>
       </c>
       <c r="N77">
-        <v>-159.471565</v>
+        <v>-162.5485192</v>
       </c>
       <c r="O77">
-        <v>-35.88110212500001</v>
+        <v>-36.57341682000001</v>
       </c>
       <c r="P77">
-        <v>-123.590462875</v>
+        <v>-125.97510238</v>
       </c>
       <c r="Q77">
-        <v>-98.39046287500003</v>
+        <v>-100.77510238</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5335379250367408</v>
+        <v>0.5538603385799383</v>
       </c>
       <c r="T77">
-        <v>3.400724664138526</v>
+        <v>3.542421525144298</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06951679683759998</v>
+        <v>0.06860210214236841</v>
       </c>
       <c r="W77">
-        <v>0.2194079393056939</v>
+        <v>0.2196236243148295</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3089635415004444</v>
+        <v>0.3048982317438597</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2998404357384556</v>
+        <v>0.3017404357384556</v>
       </c>
       <c r="C78">
-        <v>-276.0780697570194</v>
+        <v>-294.3194781532437</v>
       </c>
       <c r="D78">
-        <v>699.4459302429806</v>
+        <v>694.2535218467564</v>
       </c>
       <c r="E78">
-        <v>466.524</v>
+        <v>479.5730000000001</v>
       </c>
       <c r="F78">
-        <v>991.724</v>
+        <v>1004.773</v>
       </c>
       <c r="G78">
         <v>16.2</v>
@@ -7677,37 +7677,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M78">
-        <v>233.8485192</v>
+        <v>236.9254734</v>
       </c>
       <c r="N78">
-        <v>-162.5485192</v>
+        <v>-165.6254734</v>
       </c>
       <c r="O78">
-        <v>-36.57341682000001</v>
+        <v>-37.26573151500001</v>
       </c>
       <c r="P78">
-        <v>-125.97510238</v>
+        <v>-128.359741885</v>
       </c>
       <c r="Q78">
-        <v>-100.77510238</v>
+        <v>-103.159741885</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5538603385799383</v>
+        <v>0.5759499185181963</v>
       </c>
       <c r="T78">
-        <v>3.542421525144298</v>
+        <v>3.696439852324484</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06860210214236841</v>
+        <v>0.06771116575090907</v>
       </c>
       <c r="W78">
-        <v>0.2196236243148295</v>
+        <v>0.2198337071159356</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3048982317438597</v>
+        <v>0.3009385144484847</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3017404357384556</v>
+        <v>0.3036404357384557</v>
       </c>
       <c r="C79">
-        <v>-294.3194781532437</v>
+        <v>-312.4843618885897</v>
       </c>
       <c r="D79">
-        <v>694.2535218467564</v>
+        <v>689.1376381114104</v>
       </c>
       <c r="E79">
-        <v>479.5730000000001</v>
+        <v>492.6220000000001</v>
       </c>
       <c r="F79">
-        <v>1004.773</v>
+        <v>1017.822</v>
       </c>
       <c r="G79">
         <v>16.2</v>
@@ -7759,37 +7759,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M79">
-        <v>236.9254734</v>
+        <v>240.0024276</v>
       </c>
       <c r="N79">
-        <v>-165.6254734</v>
+        <v>-168.7024276</v>
       </c>
       <c r="O79">
-        <v>-37.26573151500001</v>
+        <v>-37.95804621000001</v>
       </c>
       <c r="P79">
-        <v>-128.359741885</v>
+        <v>-130.74438139</v>
       </c>
       <c r="Q79">
-        <v>-103.159741885</v>
+        <v>-105.54438139</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5759499185181963</v>
+        <v>0.6000476420872054</v>
       </c>
       <c r="T79">
-        <v>3.696439852324484</v>
+        <v>3.864459845611961</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06771116575090907</v>
+        <v>0.06684307388230769</v>
       </c>
       <c r="W79">
-        <v>0.2198337071159356</v>
+        <v>0.2200384031785519</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3009385144484847</v>
+        <v>0.2970803283658119</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3036404357384557</v>
+        <v>0.3055404357384557</v>
       </c>
       <c r="C80">
-        <v>-312.4843618885897</v>
+        <v>-330.574400295602</v>
       </c>
       <c r="D80">
-        <v>689.1376381114104</v>
+        <v>684.096599704398</v>
       </c>
       <c r="E80">
-        <v>492.6220000000001</v>
+        <v>505.671</v>
       </c>
       <c r="F80">
-        <v>1017.822</v>
+        <v>1030.871</v>
       </c>
       <c r="G80">
         <v>16.2</v>
@@ -7841,37 +7841,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M80">
-        <v>240.0024276</v>
+        <v>243.0793818</v>
       </c>
       <c r="N80">
-        <v>-168.7024276</v>
+        <v>-171.7793818</v>
       </c>
       <c r="O80">
-        <v>-37.95804621000001</v>
+        <v>-38.65036090500001</v>
       </c>
       <c r="P80">
-        <v>-130.74438139</v>
+        <v>-133.129020895</v>
       </c>
       <c r="Q80">
-        <v>-105.54438139</v>
+        <v>-107.929020895</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6000476420872054</v>
+        <v>0.626440386948501</v>
       </c>
       <c r="T80">
-        <v>3.864459845611961</v>
+        <v>4.048481743022055</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06684307388230769</v>
+        <v>0.06599695902303797</v>
       </c>
       <c r="W80">
-        <v>0.2200384031785519</v>
+        <v>0.2202379170623677</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2970803283658119</v>
+        <v>0.2933198178801687</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3055404357384557</v>
+        <v>0.3074404357384556</v>
       </c>
       <c r="C81">
-        <v>-330.574400295602</v>
+        <v>-348.5912239264175</v>
       </c>
       <c r="D81">
-        <v>684.096599704398</v>
+        <v>679.1287760735826</v>
       </c>
       <c r="E81">
-        <v>505.671</v>
+        <v>518.72</v>
       </c>
       <c r="F81">
-        <v>1030.871</v>
+        <v>1043.92</v>
       </c>
       <c r="G81">
         <v>16.2</v>
@@ -7923,37 +7923,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M81">
-        <v>243.0793818</v>
+        <v>246.156336</v>
       </c>
       <c r="N81">
-        <v>-171.7793818</v>
+        <v>-174.856336</v>
       </c>
       <c r="O81">
-        <v>-38.65036090500001</v>
+        <v>-39.34267560000001</v>
       </c>
       <c r="P81">
-        <v>-133.129020895</v>
+        <v>-135.5136604</v>
       </c>
       <c r="Q81">
-        <v>-107.929020895</v>
+        <v>-110.3136604</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.626440386948501</v>
+        <v>0.6554724062959261</v>
       </c>
       <c r="T81">
-        <v>4.048481743022055</v>
+        <v>4.250905830173158</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06599695902303797</v>
+        <v>0.06517199703524999</v>
       </c>
       <c r="W81">
-        <v>0.2202379170623677</v>
+        <v>0.220432443099088</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2933198178801687</v>
+        <v>0.2896533201566666</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3074404357384556</v>
+        <v>0.3093404357384556</v>
       </c>
       <c r="C82">
-        <v>-348.5912239264175</v>
+        <v>-366.5364163111803</v>
       </c>
       <c r="D82">
-        <v>679.1287760735826</v>
+        <v>674.2325836888197</v>
       </c>
       <c r="E82">
-        <v>518.72</v>
+        <v>531.769</v>
       </c>
       <c r="F82">
-        <v>1043.92</v>
+        <v>1056.969</v>
       </c>
       <c r="G82">
         <v>16.2</v>
@@ -8005,37 +8005,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M82">
-        <v>246.156336</v>
+        <v>249.2332902</v>
       </c>
       <c r="N82">
-        <v>-174.856336</v>
+        <v>-177.9332902</v>
       </c>
       <c r="O82">
-        <v>-39.34267560000001</v>
+        <v>-40.03499029500001</v>
       </c>
       <c r="P82">
-        <v>-135.5136604</v>
+        <v>-137.898299905</v>
       </c>
       <c r="Q82">
-        <v>-110.3136604</v>
+        <v>-112.698299905</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6554724062959261</v>
+        <v>0.6875604276799222</v>
       </c>
       <c r="T82">
-        <v>4.250905830173158</v>
+        <v>4.474637715971745</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06517199703524999</v>
+        <v>0.06436740447925926</v>
       </c>
       <c r="W82">
-        <v>0.220432443099088</v>
+        <v>0.2206221660237907</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2896533201566666</v>
+        <v>0.2860773532411522</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3093404357384556</v>
+        <v>0.3112404357384556</v>
       </c>
       <c r="C83">
-        <v>-366.5364163111803</v>
+        <v>-384.4115156409415</v>
       </c>
       <c r="D83">
-        <v>674.2325836888197</v>
+        <v>669.4064843590587</v>
       </c>
       <c r="E83">
-        <v>531.769</v>
+        <v>544.8180000000002</v>
       </c>
       <c r="F83">
-        <v>1056.969</v>
+        <v>1070.018</v>
       </c>
       <c r="G83">
         <v>16.2</v>
@@ -8087,37 +8087,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M83">
-        <v>249.2332902</v>
+        <v>252.3102444000001</v>
       </c>
       <c r="N83">
-        <v>-177.9332902</v>
+        <v>-181.0102444000001</v>
       </c>
       <c r="O83">
-        <v>-40.03499029500001</v>
+        <v>-40.72730499000001</v>
       </c>
       <c r="P83">
-        <v>-137.898299905</v>
+        <v>-140.28293941</v>
       </c>
       <c r="Q83">
-        <v>-112.698299905</v>
+        <v>-115.0829394100001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6875604276799222</v>
+        <v>0.7232137847732512</v>
       </c>
       <c r="T83">
-        <v>4.474637715971745</v>
+        <v>4.723228700192398</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06436740447925926</v>
+        <v>0.06358243613195121</v>
       </c>
       <c r="W83">
-        <v>0.2206221660237907</v>
+        <v>0.2208072615600859</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2860773532411522</v>
+        <v>0.2825886050308942</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3112404357384556</v>
+        <v>0.3131404357384556</v>
       </c>
       <c r="C84">
-        <v>-384.4115156409415</v>
+        <v>-402.2180163787891</v>
       </c>
       <c r="D84">
-        <v>669.4064843590587</v>
+        <v>664.6489836212111</v>
       </c>
       <c r="E84">
-        <v>544.8180000000002</v>
+        <v>557.8670000000002</v>
       </c>
       <c r="F84">
-        <v>1070.018</v>
+        <v>1083.067</v>
       </c>
       <c r="G84">
         <v>16.2</v>
@@ -8169,37 +8169,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M84">
-        <v>252.3102444000001</v>
+        <v>255.3871986000001</v>
       </c>
       <c r="N84">
-        <v>-181.0102444000001</v>
+        <v>-184.0871986000001</v>
       </c>
       <c r="O84">
-        <v>-40.72730499000001</v>
+        <v>-41.41961968500001</v>
       </c>
       <c r="P84">
-        <v>-140.28293941</v>
+        <v>-142.667578915</v>
       </c>
       <c r="Q84">
-        <v>-115.0829394100001</v>
+        <v>-117.467578915</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7232137847732512</v>
+        <v>0.7630616544657954</v>
       </c>
       <c r="T84">
-        <v>4.723228700192398</v>
+        <v>5.001065682556657</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06358243613195121</v>
+        <v>0.0628163826845783</v>
       </c>
       <c r="W84">
-        <v>0.2208072615600859</v>
+        <v>0.2209878969629764</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2825886050308942</v>
+        <v>0.2791839230425702</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3131404357384556</v>
+        <v>0.3150404357384557</v>
       </c>
       <c r="C85">
-        <v>-402.2180163787891</v>
+        <v>-419.9573708027698</v>
       </c>
       <c r="D85">
-        <v>664.6489836212111</v>
+        <v>659.9586291972304</v>
       </c>
       <c r="E85">
-        <v>557.8670000000002</v>
+        <v>570.9160000000002</v>
       </c>
       <c r="F85">
-        <v>1083.067</v>
+        <v>1096.116</v>
       </c>
       <c r="G85">
         <v>16.2</v>
@@ -8251,37 +8251,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M85">
-        <v>255.3871986000001</v>
+        <v>258.4641528000001</v>
       </c>
       <c r="N85">
-        <v>-184.0871986000001</v>
+        <v>-187.1641528000001</v>
       </c>
       <c r="O85">
-        <v>-41.41961968500001</v>
+        <v>-42.11193438000002</v>
       </c>
       <c r="P85">
-        <v>-142.667578915</v>
+        <v>-145.0522184200001</v>
       </c>
       <c r="Q85">
-        <v>-117.467578915</v>
+        <v>-119.8522184200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7630616544657954</v>
+        <v>0.8078905078699079</v>
       </c>
       <c r="T85">
-        <v>5.001065682556657</v>
+        <v>5.31363228771645</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0628163826845783</v>
+        <v>0.06206856860499998</v>
       </c>
       <c r="W85">
-        <v>0.2209878969629764</v>
+        <v>0.221164231522941</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2791839230425702</v>
+        <v>0.275860304911111</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3150404357384556</v>
+        <v>0.3169404357384557</v>
       </c>
       <c r="C86">
-        <v>-419.9573708027694</v>
+        <v>-437.6309904839308</v>
       </c>
       <c r="D86">
-        <v>659.9586291972305</v>
+        <v>655.3340095160692</v>
       </c>
       <c r="E86">
-        <v>570.9159999999999</v>
+        <v>583.9649999999999</v>
       </c>
       <c r="F86">
-        <v>1096.116</v>
+        <v>1109.165</v>
       </c>
       <c r="G86">
         <v>16.2</v>
@@ -8333,37 +8333,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M86">
-        <v>258.4641528</v>
+        <v>261.541107</v>
       </c>
       <c r="N86">
-        <v>-187.1641528</v>
+        <v>-190.241107</v>
       </c>
       <c r="O86">
-        <v>-42.11193438</v>
+        <v>-42.804249075</v>
       </c>
       <c r="P86">
-        <v>-145.05221842</v>
+        <v>-147.436857925</v>
       </c>
       <c r="Q86">
-        <v>-119.85221842</v>
+        <v>-122.236857925</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8078905078699072</v>
+        <v>0.8586965417279012</v>
       </c>
       <c r="T86">
-        <v>5.313632287716445</v>
+        <v>5.667874440230876</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06206856860499999</v>
+        <v>0.06133835015082352</v>
       </c>
       <c r="W86">
-        <v>0.221164231522941</v>
+        <v>0.2213364170344358</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2758603049111111</v>
+        <v>0.2726148895592156</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3169404357384557</v>
+        <v>0.3188404357384557</v>
       </c>
       <c r="C87">
-        <v>-437.6309904839308</v>
+        <v>-455.2402477026575</v>
       </c>
       <c r="D87">
-        <v>655.3340095160692</v>
+        <v>650.7737522973426</v>
       </c>
       <c r="E87">
-        <v>583.9649999999999</v>
+        <v>597.0140000000001</v>
       </c>
       <c r="F87">
-        <v>1109.165</v>
+        <v>1122.214</v>
       </c>
       <c r="G87">
         <v>16.2</v>
@@ -8415,37 +8415,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M87">
-        <v>261.541107</v>
+        <v>264.6180612000001</v>
       </c>
       <c r="N87">
-        <v>-190.241107</v>
+        <v>-193.3180612</v>
       </c>
       <c r="O87">
-        <v>-42.804249075</v>
+        <v>-43.49656377000001</v>
       </c>
       <c r="P87">
-        <v>-147.436857925</v>
+        <v>-149.82149743</v>
       </c>
       <c r="Q87">
-        <v>-122.236857925</v>
+        <v>-124.62149743</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8586965417279012</v>
+        <v>0.9167605804227512</v>
       </c>
       <c r="T87">
-        <v>5.667874440230876</v>
+        <v>6.072722614533081</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06133835015082352</v>
+        <v>0.06062511352116278</v>
       </c>
       <c r="W87">
-        <v>0.2213364170344358</v>
+        <v>0.2215045982317098</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2726148895592156</v>
+        <v>0.2694449489829457</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3188404357384557</v>
+        <v>0.3207404357384556</v>
       </c>
       <c r="C88">
-        <v>-455.2402477026575</v>
+        <v>-472.7864768062775</v>
       </c>
       <c r="D88">
-        <v>650.7737522973426</v>
+        <v>646.2765231937226</v>
       </c>
       <c r="E88">
-        <v>597.0140000000001</v>
+        <v>610.0630000000001</v>
       </c>
       <c r="F88">
-        <v>1122.214</v>
+        <v>1135.263</v>
       </c>
       <c r="G88">
         <v>16.2</v>
@@ -8497,37 +8497,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M88">
-        <v>264.6180612000001</v>
+        <v>267.6950154</v>
       </c>
       <c r="N88">
-        <v>-193.3180612</v>
+        <v>-196.3950154</v>
       </c>
       <c r="O88">
-        <v>-43.49656377000001</v>
+        <v>-44.18887846500001</v>
       </c>
       <c r="P88">
-        <v>-149.82149743</v>
+        <v>-152.206136935</v>
       </c>
       <c r="Q88">
-        <v>-124.62149743</v>
+        <v>-127.006136935</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9167605804227512</v>
+        <v>0.9837575481475782</v>
       </c>
       <c r="T88">
-        <v>6.072722614533081</v>
+        <v>6.539855123343318</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06062511352116278</v>
+        <v>0.05992827313586205</v>
       </c>
       <c r="W88">
-        <v>0.2215045982317098</v>
+        <v>0.2216689131945637</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2694449489829457</v>
+        <v>0.2663478806038314</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3207404357384556</v>
+        <v>0.3226404357384557</v>
       </c>
       <c r="C89">
-        <v>-472.7864768062775</v>
+        <v>-490.2709755107666</v>
       </c>
       <c r="D89">
-        <v>646.2765231937226</v>
+        <v>641.8410244892335</v>
       </c>
       <c r="E89">
-        <v>610.0630000000001</v>
+        <v>623.1120000000001</v>
       </c>
       <c r="F89">
-        <v>1135.263</v>
+        <v>1148.312</v>
       </c>
       <c r="G89">
         <v>16.2</v>
@@ -8579,37 +8579,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M89">
-        <v>267.6950154</v>
+        <v>270.7719696</v>
       </c>
       <c r="N89">
-        <v>-196.3950154</v>
+        <v>-199.4719696</v>
       </c>
       <c r="O89">
-        <v>-44.18887846500001</v>
+        <v>-44.88119316000001</v>
       </c>
       <c r="P89">
-        <v>-152.206136935</v>
+        <v>-154.59077644</v>
       </c>
       <c r="Q89">
-        <v>-127.006136935</v>
+        <v>-129.39077644</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9837575481475782</v>
+        <v>1.061920677159877</v>
       </c>
       <c r="T89">
-        <v>6.539855123343318</v>
+        <v>7.084843050288596</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05992827313586205</v>
+        <v>0.05924727003204545</v>
       </c>
       <c r="W89">
-        <v>0.2216689131945637</v>
+        <v>0.2218294937264437</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2663478806038314</v>
+        <v>0.2633212001424242</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3226404357384557</v>
+        <v>0.3245404357384557</v>
       </c>
       <c r="C90">
-        <v>-490.2709755107666</v>
+        <v>-507.6950061492126</v>
       </c>
       <c r="D90">
-        <v>641.8410244892335</v>
+        <v>637.4659938507874</v>
       </c>
       <c r="E90">
-        <v>623.1120000000001</v>
+        <v>636.1610000000001</v>
       </c>
       <c r="F90">
-        <v>1148.312</v>
+        <v>1161.361</v>
       </c>
       <c r="G90">
         <v>16.2</v>
@@ -8661,37 +8661,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M90">
-        <v>270.7719696</v>
+        <v>273.8489238</v>
       </c>
       <c r="N90">
-        <v>-199.4719696</v>
+        <v>-202.5489238</v>
       </c>
       <c r="O90">
-        <v>-44.88119316000001</v>
+        <v>-45.573507855</v>
       </c>
       <c r="P90">
-        <v>-154.59077644</v>
+        <v>-156.975415945</v>
       </c>
       <c r="Q90">
-        <v>-129.39077644</v>
+        <v>-131.775415945</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.061920677159877</v>
+        <v>1.154295284174411</v>
       </c>
       <c r="T90">
-        <v>7.084843050288596</v>
+        <v>7.728919691223923</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05924727003204545</v>
+        <v>0.05858157036876404</v>
       </c>
       <c r="W90">
-        <v>0.2218294937264437</v>
+        <v>0.2219864657070455</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2633212001424242</v>
+        <v>0.2603625349722846</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3245404357384557</v>
+        <v>0.3264404357384557</v>
       </c>
       <c r="C91">
-        <v>-507.6950061492126</v>
+        <v>-525.0597968695679</v>
       </c>
       <c r="D91">
-        <v>637.4659938507874</v>
+        <v>633.1502031304321</v>
       </c>
       <c r="E91">
-        <v>636.1610000000001</v>
+        <v>649.21</v>
       </c>
       <c r="F91">
-        <v>1161.361</v>
+        <v>1174.41</v>
       </c>
       <c r="G91">
         <v>16.2</v>
@@ -8743,37 +8743,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M91">
-        <v>273.8489238</v>
+        <v>276.925878</v>
       </c>
       <c r="N91">
-        <v>-202.5489238</v>
+        <v>-205.625878</v>
       </c>
       <c r="O91">
-        <v>-45.573507855</v>
+        <v>-46.26582255</v>
       </c>
       <c r="P91">
-        <v>-156.975415945</v>
+        <v>-159.36005545</v>
       </c>
       <c r="Q91">
-        <v>-131.775415945</v>
+        <v>-134.16005545</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.154295284174411</v>
+        <v>1.265144812591852</v>
       </c>
       <c r="T91">
-        <v>7.728919691223923</v>
+        <v>8.501811660346316</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05858157036876404</v>
+        <v>0.05793066403133334</v>
       </c>
       <c r="W91">
-        <v>0.2219864657070455</v>
+        <v>0.2221399494214116</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2603625349722846</v>
+        <v>0.257469617917037</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3264404357384557</v>
+        <v>0.3283404357384556</v>
       </c>
       <c r="C92">
-        <v>-525.0597968695679</v>
+        <v>-542.3665427840724</v>
       </c>
       <c r="D92">
-        <v>633.1502031304321</v>
+        <v>628.8924572159276</v>
       </c>
       <c r="E92">
-        <v>649.21</v>
+        <v>662.259</v>
       </c>
       <c r="F92">
-        <v>1174.41</v>
+        <v>1187.459</v>
       </c>
       <c r="G92">
         <v>16.2</v>
@@ -8825,37 +8825,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M92">
-        <v>276.925878</v>
+        <v>280.0028322</v>
       </c>
       <c r="N92">
-        <v>-205.625878</v>
+        <v>-208.7028322</v>
       </c>
       <c r="O92">
-        <v>-46.26582255</v>
+        <v>-46.958137245</v>
       </c>
       <c r="P92">
-        <v>-159.36005545</v>
+        <v>-161.744694955</v>
       </c>
       <c r="Q92">
-        <v>-134.16005545</v>
+        <v>-136.544694955</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.265144812591852</v>
+        <v>1.400627569546502</v>
       </c>
       <c r="T92">
-        <v>8.501811660346316</v>
+        <v>9.446457400384796</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05793066403133334</v>
+        <v>0.05729406332769231</v>
       </c>
       <c r="W92">
-        <v>0.2221399494214116</v>
+        <v>0.2222900598673302</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.257469617917037</v>
+        <v>0.2546402814564103</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3283404357384556</v>
+        <v>0.3302404357384556</v>
       </c>
       <c r="C93">
-        <v>-542.3665427840724</v>
+        <v>-559.6164070726118</v>
       </c>
       <c r="D93">
-        <v>628.8924572159276</v>
+        <v>624.6915929273882</v>
       </c>
       <c r="E93">
-        <v>662.259</v>
+        <v>675.308</v>
       </c>
       <c r="F93">
-        <v>1187.459</v>
+        <v>1200.508</v>
       </c>
       <c r="G93">
         <v>16.2</v>
@@ -8907,37 +8907,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M93">
-        <v>280.0028322</v>
+        <v>283.0797864</v>
       </c>
       <c r="N93">
-        <v>-208.7028322</v>
+        <v>-211.7797864</v>
       </c>
       <c r="O93">
-        <v>-46.958137245</v>
+        <v>-47.65045194000001</v>
       </c>
       <c r="P93">
-        <v>-161.744694955</v>
+        <v>-164.12933446</v>
       </c>
       <c r="Q93">
-        <v>-136.544694955</v>
+        <v>-138.92933446</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.400627569546502</v>
+        <v>1.569981015739816</v>
       </c>
       <c r="T93">
-        <v>9.446457400384796</v>
+        <v>10.6272645754329</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05729406332769231</v>
+        <v>0.0566713017697826</v>
       </c>
       <c r="W93">
-        <v>0.2222900598673302</v>
+        <v>0.2224369070426853</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2546402814564103</v>
+        <v>0.2518724523101449</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3302404357384556</v>
+        <v>0.3321404357384556</v>
       </c>
       <c r="C94">
-        <v>-559.6164070726118</v>
+        <v>-576.810522042145</v>
       </c>
       <c r="D94">
-        <v>624.6915929273882</v>
+        <v>620.5464779578552</v>
       </c>
       <c r="E94">
-        <v>675.308</v>
+        <v>688.3570000000002</v>
       </c>
       <c r="F94">
-        <v>1200.508</v>
+        <v>1213.557</v>
       </c>
       <c r="G94">
         <v>16.2</v>
@@ -8989,37 +8989,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M94">
-        <v>283.0797864</v>
+        <v>286.1567406000001</v>
       </c>
       <c r="N94">
-        <v>-211.7797864</v>
+        <v>-214.8567406000001</v>
       </c>
       <c r="O94">
-        <v>-47.65045194000001</v>
+        <v>-48.34276663500002</v>
       </c>
       <c r="P94">
-        <v>-164.12933446</v>
+        <v>-166.513973965</v>
       </c>
       <c r="Q94">
-        <v>-138.92933446</v>
+        <v>-141.3139739650001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.569981015739816</v>
+        <v>1.787721160845504</v>
       </c>
       <c r="T94">
-        <v>10.6272645754329</v>
+        <v>12.14544522906617</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0566713017697826</v>
+        <v>0.05606193293354837</v>
       </c>
       <c r="W94">
-        <v>0.2224369070426853</v>
+        <v>0.2225805962142693</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2518724523101449</v>
+        <v>0.2491641463713261</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3321404357384556</v>
+        <v>0.3340404357384557</v>
       </c>
       <c r="C95">
-        <v>-576.810522042145</v>
+        <v>-593.9499901442323</v>
       </c>
       <c r="D95">
-        <v>620.5464779578552</v>
+        <v>616.4560098557679</v>
       </c>
       <c r="E95">
-        <v>688.3570000000002</v>
+        <v>701.4060000000002</v>
       </c>
       <c r="F95">
-        <v>1213.557</v>
+        <v>1226.606</v>
       </c>
       <c r="G95">
         <v>16.2</v>
@@ -9071,37 +9071,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M95">
-        <v>286.1567406000001</v>
+        <v>289.2336948000001</v>
       </c>
       <c r="N95">
-        <v>-214.8567406000001</v>
+        <v>-217.9336948000001</v>
       </c>
       <c r="O95">
-        <v>-48.34276663500002</v>
+        <v>-49.03508133000002</v>
       </c>
       <c r="P95">
-        <v>-166.513973965</v>
+        <v>-168.89861347</v>
       </c>
       <c r="Q95">
-        <v>-141.3139739650001</v>
+        <v>-143.6986134700001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.787721160845504</v>
+        <v>2.078041354319755</v>
       </c>
       <c r="T95">
-        <v>12.14544522906617</v>
+        <v>14.1696861005772</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05606193293354837</v>
+        <v>0.05546552939170211</v>
       </c>
       <c r="W95">
-        <v>0.2225805962142693</v>
+        <v>0.2227212281694367</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2491641463713261</v>
+        <v>0.2465134639631205</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3340404357384557</v>
+        <v>0.3359404357384557</v>
       </c>
       <c r="C96">
-        <v>-593.9499901442323</v>
+        <v>-611.0358849525858</v>
       </c>
       <c r="D96">
-        <v>616.4560098557679</v>
+        <v>612.4191150474144</v>
       </c>
       <c r="E96">
-        <v>701.4060000000002</v>
+        <v>714.4550000000002</v>
       </c>
       <c r="F96">
-        <v>1226.606</v>
+        <v>1239.655</v>
       </c>
       <c r="G96">
         <v>16.2</v>
@@ -9153,37 +9153,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M96">
-        <v>289.2336948000001</v>
+        <v>292.3106490000001</v>
       </c>
       <c r="N96">
-        <v>-217.9336948000001</v>
+        <v>-221.0106490000001</v>
       </c>
       <c r="O96">
-        <v>-49.03508133000002</v>
+        <v>-49.72739602500001</v>
       </c>
       <c r="P96">
-        <v>-168.89861347</v>
+        <v>-171.283252975</v>
       </c>
       <c r="Q96">
-        <v>-143.6986134700001</v>
+        <v>-146.0832529750001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.078041354319755</v>
+        <v>2.484489625183707</v>
       </c>
       <c r="T96">
-        <v>14.1696861005772</v>
+        <v>17.00362332069265</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05546552939170211</v>
+        <v>0.05488168171389472</v>
       </c>
       <c r="W96">
-        <v>0.2227212281694367</v>
+        <v>0.2228588994518636</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2465134639631205</v>
+        <v>0.2439185853950877</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3359404357384557</v>
+        <v>0.3378404357384556</v>
       </c>
       <c r="C97">
-        <v>-611.0358849525858</v>
+        <v>-628.0692521024558</v>
       </c>
       <c r="D97">
-        <v>612.4191150474144</v>
+        <v>608.4347478975443</v>
       </c>
       <c r="E97">
-        <v>714.4550000000002</v>
+        <v>727.5040000000001</v>
       </c>
       <c r="F97">
-        <v>1239.655</v>
+        <v>1252.704</v>
       </c>
       <c r="G97">
         <v>16.2</v>
@@ -9235,37 +9235,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M97">
-        <v>292.3106490000001</v>
+        <v>295.3876032000001</v>
       </c>
       <c r="N97">
-        <v>-221.0106490000001</v>
+        <v>-224.0876032</v>
       </c>
       <c r="O97">
-        <v>-49.72739602500001</v>
+        <v>-50.41971072000001</v>
       </c>
       <c r="P97">
-        <v>-171.283252975</v>
+        <v>-173.66789248</v>
       </c>
       <c r="Q97">
-        <v>-146.0832529750001</v>
+        <v>-148.46789248</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.484489625183707</v>
+        <v>3.094162031479635</v>
       </c>
       <c r="T97">
-        <v>17.00362332069265</v>
+        <v>21.25452915086582</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05488168171389472</v>
+        <v>0.05430999752937499</v>
       </c>
       <c r="W97">
-        <v>0.2228588994518636</v>
+        <v>0.2229937025825734</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2439185853950877</v>
+        <v>0.2413777667972221</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3378404357384556</v>
+        <v>0.3397404357384556</v>
       </c>
       <c r="C98">
-        <v>-628.0692521024556</v>
+        <v>-645.0511101935896</v>
       </c>
       <c r="D98">
-        <v>608.4347478975443</v>
+        <v>604.5018898064105</v>
       </c>
       <c r="E98">
-        <v>727.5039999999999</v>
+        <v>740.5530000000001</v>
       </c>
       <c r="F98">
-        <v>1252.704</v>
+        <v>1265.753</v>
       </c>
       <c r="G98">
         <v>16.2</v>
@@ -9317,37 +9317,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M98">
-        <v>295.3876032</v>
+        <v>298.4645574</v>
       </c>
       <c r="N98">
-        <v>-224.0876032</v>
+        <v>-227.1645574</v>
       </c>
       <c r="O98">
-        <v>-50.41971072</v>
+        <v>-51.11202541500001</v>
       </c>
       <c r="P98">
-        <v>-173.66789248</v>
+        <v>-176.052531985</v>
       </c>
       <c r="Q98">
-        <v>-148.46789248</v>
+        <v>-150.852531985</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.094162031479627</v>
+        <v>4.110282708639503</v>
       </c>
       <c r="T98">
-        <v>21.25452915086577</v>
+        <v>28.33937220115436</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.054309997529375</v>
+        <v>0.05375010064762886</v>
       </c>
       <c r="W98">
-        <v>0.2229937025825734</v>
+        <v>0.2231257262672891</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2413777667972222</v>
+        <v>0.2388893362116838</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3397404357384556</v>
+        <v>0.3416404357384556</v>
       </c>
       <c r="C99">
-        <v>-645.0511101935896</v>
+        <v>-661.9824516583905</v>
       </c>
       <c r="D99">
-        <v>604.5018898064105</v>
+        <v>600.6195483416096</v>
       </c>
       <c r="E99">
-        <v>740.5530000000001</v>
+        <v>753.6020000000001</v>
       </c>
       <c r="F99">
-        <v>1265.753</v>
+        <v>1278.802</v>
       </c>
       <c r="G99">
         <v>16.2</v>
@@ -9399,37 +9399,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M99">
-        <v>298.4645574</v>
+        <v>301.5415116</v>
       </c>
       <c r="N99">
-        <v>-227.1645574</v>
+        <v>-230.2415116</v>
       </c>
       <c r="O99">
-        <v>-51.11202541500001</v>
+        <v>-51.80434011000001</v>
       </c>
       <c r="P99">
-        <v>-176.052531985</v>
+        <v>-178.43717149</v>
       </c>
       <c r="Q99">
-        <v>-150.852531985</v>
+        <v>-153.23717149</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.110282708639503</v>
+        <v>6.142524062959254</v>
       </c>
       <c r="T99">
-        <v>28.33937220115436</v>
+        <v>42.50905830173154</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05375010064762886</v>
+        <v>0.05320163023285714</v>
       </c>
       <c r="W99">
-        <v>0.2231257262672891</v>
+        <v>0.2232550555910923</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2388893362116838</v>
+        <v>0.2364516899238095</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3416404357384556</v>
+        <v>0.3435404357384557</v>
       </c>
       <c r="C100">
-        <v>-661.9824516583905</v>
+        <v>-678.8642435968409</v>
       </c>
       <c r="D100">
-        <v>600.6195483416096</v>
+        <v>596.7867564031592</v>
       </c>
       <c r="E100">
-        <v>753.6020000000001</v>
+        <v>766.6510000000001</v>
       </c>
       <c r="F100">
-        <v>1278.802</v>
+        <v>1291.851</v>
       </c>
       <c r="G100">
         <v>16.2</v>
@@ -9481,37 +9481,37 @@
         <v>71.30000000000001</v>
       </c>
       <c r="M100">
-        <v>301.5415116</v>
+        <v>304.6184658</v>
       </c>
       <c r="N100">
-        <v>-230.2415116</v>
+        <v>-233.3184658</v>
       </c>
       <c r="O100">
-        <v>-51.80434011000001</v>
+        <v>-52.49665480500001</v>
       </c>
       <c r="P100">
-        <v>-178.43717149</v>
+        <v>-180.821810995</v>
       </c>
       <c r="Q100">
-        <v>-153.23717149</v>
+        <v>-155.621810995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.142524062959254</v>
+        <v>12.23924812591851</v>
       </c>
       <c r="T100">
-        <v>42.50905830173154</v>
+        <v>85.01811660346307</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05320163023285714</v>
+        <v>0.05266424002848485</v>
       </c>
       <c r="W100">
-        <v>0.2232550555910923</v>
+        <v>0.2233817722012833</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2364516899238095</v>
+        <v>0.2340632890154882</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3435404357384557</v>
-      </c>
-      <c r="C101">
-        <v>-678.8642435968409</v>
-      </c>
-      <c r="D101">
-        <v>596.7867564031592</v>
-      </c>
-      <c r="E101">
-        <v>766.6510000000001</v>
-      </c>
-      <c r="F101">
-        <v>1291.851</v>
-      </c>
-      <c r="G101">
-        <v>16.2</v>
-      </c>
-      <c r="H101">
-        <v>779.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>96.5</v>
-      </c>
-      <c r="K101">
-        <v>25.2</v>
-      </c>
-      <c r="L101">
-        <v>71.30000000000001</v>
-      </c>
-      <c r="M101">
-        <v>304.6184658</v>
-      </c>
-      <c r="N101">
-        <v>-233.3184658</v>
-      </c>
-      <c r="O101">
-        <v>-52.49665480500001</v>
-      </c>
-      <c r="P101">
-        <v>-180.821810995</v>
-      </c>
-      <c r="Q101">
-        <v>-155.621810995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.23924812591851</v>
-      </c>
-      <c r="T101">
-        <v>85.01811660346307</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05266424002848485</v>
-      </c>
-      <c r="W101">
-        <v>0.2233817722012833</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2340632890154882</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
